--- a/dev_docs/Tetra数值公式_26_4_4.xlsx
+++ b/dev_docs/Tetra数值公式_26_4_4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E95290-08BF-4DFD-AC33-CDB36631A29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F8F068-7C98-4D1D-ADA0-701B89F0C54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="332">
   <si>
     <t>刀刃</t>
   </si>
@@ -649,9 +649,6 @@
     <t>炎狱尖塔块</t>
   </si>
   <si>
-    <t>火焰伤害+1.5</t>
-  </si>
-  <si>
     <t>'enderio:vibrant_alloy_ingot'</t>
   </si>
   <si>
@@ -763,9 +760,6 @@
     <t>极限合金</t>
   </si>
   <si>
-    <t>盔甲撕裂+5%</t>
-  </si>
-  <si>
     <t>2.2.2</t>
   </si>
   <si>
@@ -793,12 +787,6 @@
     <t>中子</t>
   </si>
   <si>
-    <t>移动速度-5%</t>
-  </si>
-  <si>
-    <t>攻击伤害+3%</t>
-  </si>
-  <si>
     <t>2.2.3</t>
   </si>
   <si>
@@ -811,12 +799,6 @@
     <t>生命值+3%</t>
   </si>
   <si>
-    <t>盔甲撕裂+3%</t>
-  </si>
-  <si>
-    <t>招架治疗量+333</t>
-  </si>
-  <si>
     <t>kubejs:coil_of_sorrow'</t>
   </si>
   <si>
@@ -832,21 +814,15 @@
     <t>2.2.4</t>
   </si>
   <si>
-    <t>kubejs:beryllium_bronze_alloy_ingot</t>
-  </si>
-  <si>
-    <t>铍青铜合金</t>
+    <t>kubejs:menril-silicon_sic_sic_cmc_ingot'</t>
+  </si>
+  <si>
+    <t>铍青铜复合材料</t>
   </si>
   <si>
     <t>韧性+1</t>
   </si>
   <si>
-    <t>癫火抵抗+0.1</t>
-  </si>
-  <si>
-    <t>暴击率+0.035</t>
-  </si>
-  <si>
     <t>cataclysm:void_stone'</t>
   </si>
   <si>
@@ -874,83 +850,422 @@
     <t>紫颂果结晶</t>
   </si>
   <si>
-    <t>冰霜伤害+3</t>
+    <t>2.3.1</t>
+  </si>
+  <si>
+    <t>'enderio:end_steel_ingot'</t>
+  </si>
+  <si>
+    <t>末地钢锭</t>
+  </si>
+  <si>
+    <t>特殊行动冷却+0.05</t>
+  </si>
+  <si>
+    <t>攻击伤害+1</t>
+  </si>
+  <si>
+    <t>kubejs:chorus_logic_composite_coil'</t>
+  </si>
+  <si>
+    <t>紫菘逻辑线圈</t>
+  </si>
+  <si>
+    <t>2.3.2</t>
+  </si>
+  <si>
+    <t>2.3.3</t>
+  </si>
+  <si>
+    <t>头</t>
+  </si>
+  <si>
+    <t>胸</t>
+  </si>
+  <si>
+    <t>腿</t>
+  </si>
+  <si>
+    <t>脚</t>
+  </si>
+  <si>
+    <t>基底</t>
+  </si>
+  <si>
+    <t>左</t>
+  </si>
+  <si>
+    <t>右</t>
+  </si>
+  <si>
+    <t>腰带</t>
+  </si>
+  <si>
+    <t>原版</t>
+  </si>
+  <si>
+    <t>重型</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
+    <t>行动力消耗</t>
+  </si>
+  <si>
+    <r>
+      <t>火焰伤害+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1攻击=2总元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰伤害+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰伤害+10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>冰霜伤害+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>癫火抵抗+0.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性+0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率-0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击伤害+5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总共10+4=14部件，默认9+3=12部件，总元素伤害=x*12</t>
+  </si>
+  <si>
+    <t>暴击伤害-0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击伤害+1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>攻击伤害+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>移动速度-5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>冰霜伤害+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>火焰伤害+3</t>
-  </si>
-  <si>
-    <t>2.3.1</t>
-  </si>
-  <si>
-    <t>'enderio:end_steel_ingot'</t>
-  </si>
-  <si>
-    <t>末地钢锭</t>
-  </si>
-  <si>
-    <t>特殊行动冷却+0.05</t>
-  </si>
-  <si>
-    <t>行动力效率+8</t>
-  </si>
-  <si>
-    <t>攻击伤害+1</t>
-  </si>
-  <si>
-    <t>kubejs:chorus_logic_composite_coil'</t>
-  </si>
-  <si>
-    <t>紫菘逻辑线圈</t>
-  </si>
-  <si>
-    <t>2.3.2</t>
-  </si>
-  <si>
-    <t>2.3.3</t>
-  </si>
-  <si>
-    <t>头</t>
-  </si>
-  <si>
-    <t>胸</t>
-  </si>
-  <si>
-    <t>腿</t>
-  </si>
-  <si>
-    <t>脚</t>
-  </si>
-  <si>
-    <t>基底</t>
-  </si>
-  <si>
-    <t>左</t>
-  </si>
-  <si>
-    <t>右</t>
-  </si>
-  <si>
-    <t>腰带</t>
-  </si>
-  <si>
-    <t>原版</t>
-  </si>
-  <si>
-    <t>重型</t>
-  </si>
-  <si>
-    <t>移速</t>
-  </si>
-  <si>
-    <t>行动力消耗</t>
-  </si>
-  <si>
-    <t>kubejs:menril-silicon_sic_sic_cmc_ingot'</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>铍青铜复合材料</t>
+    <r>
+      <t>护甲穿透+1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>癫火伤害+0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>癫火伤害+0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>生命值+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>仇恨+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+0.06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>癫火抵抗+0.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>仇恨-0.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>护甲穿透+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>盔甲撕裂+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>盔甲撕裂+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害+0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜伤害+7.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>行动力效率+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜伤害+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击伤害-2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实装标记</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仇恨-30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -959,7 +1274,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.0_ "/>
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1000,7 +1315,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
+        <fgColor theme="4" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1012,7 +1327,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14990691854609822"/>
+        <fgColor theme="0" tint="-0.1498764000366222"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79985961485641044"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79985961485641044"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79985961485641044"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1024,37 +1369,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79989013336588644"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79989013336588644"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79989013336588644"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79992065187536243"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79989013336588644"/>
+        <fgColor theme="8" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1084,19 +1399,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79989013336588644"/>
+        <fgColor theme="3" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79985961485641044"/>
+        <fgColor theme="8" tint="0.79982909634693444"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79985961485641044"/>
+        <fgColor theme="9" tint="0.79982909634693444"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1128,7 +1443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1183,7 +1498,7 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1192,7 +1507,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1470,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S154"/>
+  <dimension ref="A1:X154"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="8.625" style="3" customWidth="1"/>
@@ -1481,7 +1805,7 @@
     <col min="20" max="16384" width="16.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1518,8 +1842,12 @@
       <c r="S1" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U1" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="V1" s="25"/>
+    </row>
+    <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
@@ -1564,8 +1892,14 @@
       <c r="S2" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U2" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+    </row>
+    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
@@ -1607,8 +1941,14 @@
       <c r="S3" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U3" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+    </row>
+    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
@@ -1648,7 +1988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
@@ -1681,7 +2021,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
@@ -1711,7 +2051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
@@ -1741,7 +2081,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F8" s="3" t="s">
         <v>33</v>
       </c>
@@ -1752,7 +2092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F9" s="3" t="s">
         <v>34</v>
       </c>
@@ -1766,7 +2106,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>35</v>
       </c>
@@ -1824,8 +2164,11 @@
       <c r="S10" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -1885,7 +2228,7 @@
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
     </row>
-    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="12" t="s">
         <v>50</v>
       </c>
@@ -1937,7 +2280,7 @@
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
     </row>
-    <row r="13" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="12" t="s">
         <v>50</v>
       </c>
@@ -1991,7 +2334,7 @@
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
     </row>
-    <row r="14" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>6</v>
       </c>
@@ -2051,7 +2394,7 @@
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
     </row>
-    <row r="15" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="5" t="s">
         <v>61</v>
       </c>
@@ -2105,7 +2448,7 @@
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
     </row>
-    <row r="16" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>8</v>
       </c>
@@ -4793,6 +5136,15 @@
         <f t="shared" si="31"/>
         <v>5.25</v>
       </c>
+      <c r="O63" s="9">
+        <v>3</v>
+      </c>
+      <c r="P63" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q63" s="24" t="s">
+        <v>300</v>
+      </c>
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
     </row>
@@ -4813,22 +5165,22 @@
         <v>9</v>
       </c>
       <c r="H64" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I64" s="5">
         <v>4</v>
       </c>
       <c r="J64" s="17">
         <f t="shared" ref="J64:J70" si="32">(G64*$I$2)+(H64*$I$3)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K64" s="9">
         <f t="shared" ref="K64:K70" si="33">(G64*$I$5)+(H64*$I$6)+(I64*$I$7)</f>
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="L64" s="10">
         <f t="shared" ref="L64:L70" si="34">J64+K64</f>
-        <v>28.5</v>
+        <v>26.5</v>
       </c>
       <c r="M64" s="11">
         <f t="shared" ref="M64:M70" si="35">I64*$M$2</f>
@@ -4844,8 +5196,8 @@
       <c r="P64" s="9">
         <v>4</v>
       </c>
-      <c r="Q64" s="9" t="s">
-        <v>208</v>
+      <c r="Q64" s="23" t="s">
+        <v>299</v>
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
@@ -4855,10 +5207,10 @@
         <v>203</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>57</v>
@@ -4890,7 +5242,7 @@
       </c>
       <c r="N65" s="11">
         <f t="shared" si="36"/>
-        <v>7.1999999999999993</v>
+        <v>7.2</v>
       </c>
       <c r="O65" s="9">
         <v>5</v>
@@ -4899,7 +5251,7 @@
         <v>4</v>
       </c>
       <c r="Q65" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R65" s="9"/>
       <c r="S65" s="9"/>
@@ -4909,10 +5261,10 @@
         <v>203</v>
       </c>
       <c r="D66" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>57</v>
@@ -4953,7 +5305,7 @@
         <v>4</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R66" s="9"/>
       <c r="S66" s="9"/>
@@ -4966,13 +5318,13 @@
         <v>40</v>
       </c>
       <c r="C67" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="E67" s="12" t="s">
         <v>216</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>217</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>57</v>
@@ -5013,20 +5365,20 @@
         <v>5</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R67" s="9"/>
       <c r="S67" s="9"/>
     </row>
     <row r="68" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C68" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D68" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E68" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>220</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>57</v>
@@ -5073,18 +5425,18 @@
         <v>177</v>
       </c>
       <c r="S68" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C69" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D69" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E69" s="12" t="s">
         <v>222</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>223</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>57</v>
@@ -5118,21 +5470,27 @@
         <f t="shared" si="36"/>
         <v>9</v>
       </c>
-      <c r="O69" s="9"/>
-      <c r="P69" s="9"/>
-      <c r="Q69" s="9"/>
+      <c r="O69" s="9">
+        <v>4</v>
+      </c>
+      <c r="P69" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q69" s="23" t="s">
+        <v>301</v>
+      </c>
       <c r="R69" s="9"/>
       <c r="S69" s="9"/>
     </row>
     <row r="70" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C70" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D70" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E70" s="12" t="s">
         <v>224</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>225</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>57</v>
@@ -5166,15 +5524,21 @@
         <f t="shared" si="36"/>
         <v>12</v>
       </c>
-      <c r="O70" s="9"/>
-      <c r="P70" s="9"/>
-      <c r="Q70" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="R70" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="S70" s="9"/>
+      <c r="O70" s="9">
+        <v>4</v>
+      </c>
+      <c r="P70" s="9">
+        <v>6</v>
+      </c>
+      <c r="Q70" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="R70" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="S70" s="23" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="71" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
@@ -5184,13 +5548,13 @@
         <v>45</v>
       </c>
       <c r="C71" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>57</v>
@@ -5240,13 +5604,13 @@
     </row>
     <row r="72" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C72" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D72" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>57</v>
@@ -5287,10 +5651,10 @@
         <v>6</v>
       </c>
       <c r="Q72" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R72" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S72" s="9"/>
     </row>
@@ -5302,13 +5666,13 @@
         <v>50</v>
       </c>
       <c r="C73" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="E73" s="12" t="s">
         <v>233</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>234</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>57</v>
@@ -5349,7 +5713,7 @@
         <v>6</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R73" s="9" t="s">
         <v>199</v>
@@ -5358,13 +5722,13 @@
     </row>
     <row r="74" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C74" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D74" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="E74" s="12" t="s">
         <v>236</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>237</v>
       </c>
       <c r="F74" s="12" t="s">
         <v>57</v>
@@ -5398,10 +5762,18 @@
         <f t="shared" si="41"/>
         <v>10.5</v>
       </c>
-      <c r="O74" s="9"/>
-      <c r="P74" s="9"/>
-      <c r="Q74" s="9"/>
-      <c r="R74" s="9"/>
+      <c r="O74" s="9">
+        <v>5</v>
+      </c>
+      <c r="P74" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q74" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="R74" s="23" t="s">
+        <v>305</v>
+      </c>
       <c r="S74" s="9"/>
     </row>
     <row r="75" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5412,13 +5784,13 @@
         <v>45</v>
       </c>
       <c r="C75" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="E75" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>57</v>
@@ -5458,10 +5830,12 @@
       <c r="P75" s="9">
         <v>7</v>
       </c>
-      <c r="Q75" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="R75" s="9"/>
+      <c r="Q75" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="R75" s="23" t="s">
+        <v>308</v>
+      </c>
       <c r="S75" s="9"/>
     </row>
     <row r="76" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5472,13 +5846,13 @@
         <v>60</v>
       </c>
       <c r="C76" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="E76" s="12" t="s">
         <v>242</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>243</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>57</v>
@@ -5519,20 +5893,20 @@
         <v>7</v>
       </c>
       <c r="Q76" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R76" s="9"/>
       <c r="S76" s="9"/>
     </row>
     <row r="77" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C77" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="D77" s="12" t="s">
-        <v>242</v>
-      </c>
       <c r="E77" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>57</v>
@@ -5572,11 +5946,11 @@
       <c r="P77" s="9">
         <v>7</v>
       </c>
-      <c r="Q77" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="R77" s="9" t="s">
-        <v>81</v>
+      <c r="Q77" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="R77" s="23" t="s">
+        <v>303</v>
       </c>
       <c r="S77" s="9"/>
     </row>
@@ -5588,13 +5962,13 @@
         <v>65</v>
       </c>
       <c r="C78" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>57</v>
@@ -5635,22 +6009,22 @@
         <v>8</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R78" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="S78" s="9"/>
     </row>
     <row r="79" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C79" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>57</v>
@@ -5690,8 +6064,8 @@
       <c r="P79" s="9">
         <v>8</v>
       </c>
-      <c r="Q79" s="9" t="s">
-        <v>211</v>
+      <c r="Q79" s="23" t="s">
+        <v>309</v>
       </c>
       <c r="R79" s="9" t="s">
         <v>108</v>
@@ -5700,13 +6074,13 @@
     </row>
     <row r="80" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C80" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>57</v>
@@ -5746,11 +6120,11 @@
       <c r="P80" s="9">
         <v>8</v>
       </c>
-      <c r="Q80" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="R80" s="9" t="s">
-        <v>257</v>
+      <c r="Q80" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="R80" s="23" t="s">
+        <v>310</v>
       </c>
       <c r="S80" s="9"/>
     </row>
@@ -5762,13 +6136,13 @@
         <v>70</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>57</v>
@@ -5809,24 +6183,24 @@
         <v>9</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="R81" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="S81" s="9" t="s">
-        <v>263</v>
+        <v>257</v>
+      </c>
+      <c r="R81" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="S81" s="23" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="82" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C82" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="D82" s="12" t="s">
-        <v>264</v>
-      </c>
       <c r="E82" s="12" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>57</v>
@@ -5860,21 +6234,31 @@
         <f t="shared" si="46"/>
         <v>17.399999999999999</v>
       </c>
-      <c r="O82" s="9"/>
-      <c r="P82" s="9"/>
-      <c r="Q82" s="9"/>
-      <c r="R82" s="9"/>
-      <c r="S82" s="9"/>
+      <c r="O82" s="9">
+        <v>7</v>
+      </c>
+      <c r="P82" s="9">
+        <v>9</v>
+      </c>
+      <c r="Q82" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="R82" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="S82" s="9" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="83" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="12" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>57</v>
@@ -5908,11 +6292,21 @@
         <f t="shared" si="46"/>
         <v>16.5</v>
       </c>
-      <c r="O83" s="9"/>
-      <c r="P83" s="9"/>
-      <c r="Q83" s="9"/>
-      <c r="R83" s="9"/>
-      <c r="S83" s="9"/>
+      <c r="O83" s="9">
+        <v>6</v>
+      </c>
+      <c r="P83" s="9">
+        <v>6</v>
+      </c>
+      <c r="Q83" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="R83" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="S83" s="23" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="84" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
@@ -5922,13 +6316,13 @@
         <v>75</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D84" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="E84" s="23" t="s">
-        <v>308</v>
+        <v>263</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>264</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>57</v>
@@ -5969,24 +6363,24 @@
         <v>9</v>
       </c>
       <c r="Q84" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="R84" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="S84" s="9" t="s">
-        <v>273</v>
+        <v>265</v>
+      </c>
+      <c r="R84" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="S84" s="23" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="85" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C85" s="5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>57</v>
@@ -6020,21 +6414,29 @@
         <f t="shared" si="46"/>
         <v>15</v>
       </c>
-      <c r="O85" s="9"/>
-      <c r="P85" s="9"/>
-      <c r="Q85" s="9"/>
-      <c r="R85" s="9"/>
+      <c r="O85" s="9">
+        <v>6</v>
+      </c>
+      <c r="P85" s="9">
+        <v>6</v>
+      </c>
+      <c r="Q85" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="R85" s="23" t="s">
+        <v>322</v>
+      </c>
       <c r="S85" s="9"/>
     </row>
     <row r="86" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D86" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="E86" s="5" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>57</v>
@@ -6068,9 +6470,15 @@
         <f t="shared" si="46"/>
         <v>15.75</v>
       </c>
-      <c r="O86" s="9"/>
-      <c r="P86" s="9"/>
-      <c r="Q86" s="9"/>
+      <c r="O86" s="9">
+        <v>6</v>
+      </c>
+      <c r="P86" s="9">
+        <v>8</v>
+      </c>
+      <c r="Q86" s="23" t="s">
+        <v>324</v>
+      </c>
       <c r="R86" s="9"/>
       <c r="S86" s="9"/>
     </row>
@@ -6082,13 +6490,13 @@
         <v>65</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>57</v>
@@ -6128,21 +6536,21 @@
       <c r="P87" s="9">
         <v>9</v>
       </c>
-      <c r="Q87" s="9" t="s">
-        <v>60</v>
+      <c r="Q87" s="23" t="s">
+        <v>325</v>
       </c>
       <c r="R87" s="9"/>
       <c r="S87" s="9"/>
     </row>
     <row r="88" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="12" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F88" s="12" t="s">
         <v>57</v>
@@ -6182,12 +6590,10 @@
       <c r="P88" s="9">
         <v>10</v>
       </c>
-      <c r="Q88" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="R88" s="9" t="s">
-        <v>284</v>
-      </c>
+      <c r="Q88" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="R88" s="9"/>
       <c r="S88" s="9"/>
     </row>
     <row r="89" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6198,13 +6604,13 @@
         <v>80</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>57</v>
@@ -6245,24 +6651,24 @@
         <v>10</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="R89" s="9" t="s">
-        <v>289</v>
+        <v>278</v>
+      </c>
+      <c r="R89" s="23" t="s">
+        <v>327</v>
       </c>
       <c r="S89" s="9" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C90" s="5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>57</v>
@@ -6296,11 +6702,21 @@
         <f t="shared" si="51"/>
         <v>18</v>
       </c>
-      <c r="O90" s="9"/>
-      <c r="P90" s="9"/>
-      <c r="Q90" s="9"/>
-      <c r="R90" s="9"/>
-      <c r="S90" s="9"/>
+      <c r="O90" s="9">
+        <v>8</v>
+      </c>
+      <c r="P90" s="9">
+        <v>12</v>
+      </c>
+      <c r="Q90" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="R90" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="S90" s="23" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="91" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
@@ -6310,7 +6726,7 @@
         <v>85</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
@@ -6386,7 +6802,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -8495,6 +8911,11 @@
       <c r="S154" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="U2:X2"/>
+    <mergeCell ref="U3:X3"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8503,7 +8924,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.875" customWidth="1"/>
@@ -8512,7 +8933,7 @@
     <col min="9" max="9" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>38</v>
       </c>
@@ -8544,85 +8965,81 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
-        <v>206</v>
+    <row r="2" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>204</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C2" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5">
         <v>6</v>
       </c>
       <c r="E2" s="5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F2" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="9">
-        <v>4</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>208</v>
+        <v>3</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>300</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-    </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C3" s="5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="9">
         <v>4</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>211</v>
+      <c r="H3" s="23" t="s">
+        <v>299</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C4" s="5">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="D4" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E4" s="5">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="F4" s="9">
         <v>5</v>
@@ -8631,62 +9048,58 @@
         <v>4</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" s="12">
-        <v>9</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="5">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5">
         <v>12</v>
       </c>
-      <c r="E5" s="12">
-        <v>6</v>
+      <c r="E5" s="5">
+        <v>4</v>
       </c>
       <c r="F5" s="9">
+        <v>5</v>
+      </c>
+      <c r="G5" s="9">
         <v>4</v>
       </c>
-      <c r="G5" s="9">
-        <v>5</v>
-      </c>
       <c r="H5" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-    </row>
-    <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+    </row>
+    <row r="6" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C6" s="12">
+        <v>9</v>
+      </c>
+      <c r="D6" s="12">
         <v>12</v>
       </c>
-      <c r="D6" s="12">
-        <v>5</v>
-      </c>
       <c r="E6" s="12">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="9">
         <v>4</v>
@@ -8695,498 +9108,759 @@
         <v>5</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C7" s="5">
-        <v>14</v>
-      </c>
-      <c r="D7" s="5">
-        <v>6</v>
-      </c>
-      <c r="E7" s="5">
-        <v>7</v>
+        <v>217</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+    </row>
+    <row r="7" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="12">
+        <v>12</v>
+      </c>
+      <c r="D7" s="12">
+        <v>5</v>
+      </c>
+      <c r="E7" s="12">
+        <v>6.5</v>
       </c>
       <c r="F7" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" s="9">
         <v>5</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" s="5">
-        <v>17</v>
-      </c>
-      <c r="D8" s="5">
-        <v>2</v>
-      </c>
-      <c r="E8" s="5">
-        <v>7</v>
+        <v>177</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+    </row>
+    <row r="8" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="12">
+        <v>10</v>
+      </c>
+      <c r="D8" s="12">
+        <v>5</v>
+      </c>
+      <c r="E8" s="12">
+        <v>6</v>
       </c>
       <c r="F8" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="9">
-        <v>6</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>218</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="I8" s="9"/>
       <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C9" s="12">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="D9" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="12">
         <v>8</v>
       </c>
       <c r="F9" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9" s="9">
         <v>6</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-    </row>
-    <row r="10" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H9" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+    </row>
+    <row r="10" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C10" s="5">
         <v>14</v>
       </c>
       <c r="D10" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="5">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="9">
         <v>6</v>
       </c>
       <c r="G10" s="9">
+        <v>5</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+    </row>
+    <row r="11" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" s="5">
+        <v>17</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
         <v>7</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="F11" s="9">
+        <v>6</v>
+      </c>
+      <c r="G11" s="9">
+        <v>6</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+    </row>
+    <row r="12" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C12" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="D12" s="12">
+        <v>6</v>
+      </c>
+      <c r="E12" s="12">
+        <v>8</v>
+      </c>
+      <c r="F12" s="9">
+        <v>6</v>
+      </c>
+      <c r="G12" s="9">
+        <v>6</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+    </row>
+    <row r="13" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C13" s="12">
+        <v>13</v>
+      </c>
+      <c r="D13" s="12">
+        <v>5</v>
+      </c>
+      <c r="E13" s="12">
+        <v>7</v>
+      </c>
+      <c r="F13" s="9">
+        <v>5</v>
+      </c>
+      <c r="G13" s="9">
+        <v>5</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+    </row>
+    <row r="14" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C14" s="5">
+        <v>14</v>
+      </c>
+      <c r="D14" s="5">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="F14" s="9">
+        <v>6</v>
+      </c>
+      <c r="G14" s="9">
+        <v>7</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+    </row>
+    <row r="15" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="C15" s="12">
+        <v>15</v>
+      </c>
+      <c r="D15" s="12">
+        <v>7</v>
+      </c>
+      <c r="E15" s="12">
+        <v>9.5</v>
+      </c>
+      <c r="F15" s="9">
+        <v>7</v>
+      </c>
+      <c r="G15" s="9">
+        <v>7</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="C11" s="12">
-        <v>17</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="12">
+        <v>16</v>
+      </c>
+      <c r="D16" s="12">
+        <v>10</v>
+      </c>
+      <c r="E16" s="12">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F16" s="9">
         <v>7</v>
       </c>
-      <c r="E11" s="12">
-        <v>9.5</v>
-      </c>
-      <c r="F11" s="9">
+      <c r="G16" s="9">
         <v>7</v>
       </c>
-      <c r="G11" s="9">
-        <v>7</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" s="12">
-        <v>18</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="H16" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="J16" s="9"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="5">
+        <v>20</v>
+      </c>
+      <c r="D17" s="5">
         <v>10</v>
       </c>
-      <c r="E12" s="12">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="F12" s="9">
-        <v>7</v>
-      </c>
-      <c r="G12" s="9">
-        <v>7</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-    </row>
-    <row r="13" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C13" s="5">
-        <v>20</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="E17" s="5">
         <v>10</v>
-      </c>
-      <c r="E13" s="5">
-        <v>10</v>
-      </c>
-      <c r="F13" s="9">
-        <v>8</v>
-      </c>
-      <c r="G13" s="9">
-        <v>8</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-    </row>
-    <row r="14" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C14" s="5">
-        <v>23</v>
-      </c>
-      <c r="D14" s="5">
-        <v>8</v>
-      </c>
-      <c r="E14" s="5">
-        <v>11</v>
-      </c>
-      <c r="F14" s="9">
-        <v>8</v>
-      </c>
-      <c r="G14" s="9">
-        <v>8</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C15" s="5">
-        <v>17</v>
-      </c>
-      <c r="D15" s="5">
-        <v>18</v>
-      </c>
-      <c r="E15" s="5">
-        <v>10</v>
-      </c>
-      <c r="F15" s="9">
-        <v>8</v>
-      </c>
-      <c r="G15" s="9">
-        <v>8</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="C16" s="12">
-        <v>25</v>
-      </c>
-      <c r="D16" s="12">
-        <v>9</v>
-      </c>
-      <c r="E16" s="12">
-        <v>11.5</v>
-      </c>
-      <c r="F16" s="9">
-        <v>8</v>
-      </c>
-      <c r="G16" s="9">
-        <v>9</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C17" s="5">
-        <v>27</v>
-      </c>
-      <c r="D17" s="5">
-        <v>14</v>
-      </c>
-      <c r="E17" s="5">
-        <v>12</v>
       </c>
       <c r="F17" s="9">
         <v>8</v>
       </c>
       <c r="G17" s="9">
+        <v>8</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="J17" s="9"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="5">
+        <v>23</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8</v>
+      </c>
+      <c r="E18" s="5">
+        <v>11</v>
+      </c>
+      <c r="F18" s="9">
+        <v>8</v>
+      </c>
+      <c r="G18" s="9">
+        <v>8</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" s="5">
+        <v>17</v>
+      </c>
+      <c r="D19" s="5">
+        <v>18</v>
+      </c>
+      <c r="E19" s="5">
+        <v>10</v>
+      </c>
+      <c r="F19" s="9">
+        <v>8</v>
+      </c>
+      <c r="G19" s="9">
+        <v>8</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C20" s="12">
+        <v>25</v>
+      </c>
+      <c r="D20" s="12">
         <v>9</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="E20" s="12">
+        <v>11.5</v>
+      </c>
+      <c r="F20" s="9">
+        <v>8</v>
+      </c>
+      <c r="G20" s="9">
+        <v>9</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" s="12">
+        <v>25</v>
+      </c>
+      <c r="D21" s="12">
+        <v>8</v>
+      </c>
+      <c r="E21" s="12">
+        <v>11.6</v>
+      </c>
+      <c r="F21" s="9">
+        <v>7</v>
+      </c>
+      <c r="G21" s="9">
+        <v>9</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C22" s="12">
+        <v>20</v>
+      </c>
+      <c r="D22" s="12">
+        <v>23</v>
+      </c>
+      <c r="E22" s="12">
+        <v>11</v>
+      </c>
+      <c r="F22" s="9">
+        <v>6</v>
+      </c>
+      <c r="G22" s="9">
+        <v>6</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C23" s="5">
+        <v>27</v>
+      </c>
+      <c r="D23" s="5">
+        <v>14</v>
+      </c>
+      <c r="E23" s="5">
+        <v>12</v>
+      </c>
+      <c r="F23" s="9">
+        <v>8</v>
+      </c>
+      <c r="G23" s="9">
+        <v>9</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C24" s="5">
+        <v>11</v>
+      </c>
+      <c r="D24" s="5">
+        <v>28</v>
+      </c>
+      <c r="E24" s="5">
+        <v>10</v>
+      </c>
+      <c r="F24" s="9">
+        <v>6</v>
+      </c>
+      <c r="G24" s="9">
+        <v>6</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="J24" s="9"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C25" s="5">
+        <v>10</v>
+      </c>
+      <c r="D25" s="5">
+        <v>35</v>
+      </c>
+      <c r="E25" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="F25" s="9">
+        <v>6</v>
+      </c>
+      <c r="G25" s="9">
+        <v>8</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="B26" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="C26" s="12">
+        <v>12</v>
+      </c>
+      <c r="D26" s="12">
+        <v>30</v>
+      </c>
+      <c r="E26" s="12">
+        <v>10.5</v>
+      </c>
+      <c r="F26" s="9">
+        <v>9</v>
+      </c>
+      <c r="G26" s="9">
+        <v>9</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
+      <c r="B27" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C27" s="12">
+        <v>10</v>
+      </c>
+      <c r="D27" s="12">
+        <v>15</v>
+      </c>
+      <c r="E27" s="12">
+        <v>7</v>
+      </c>
+      <c r="F27" s="9">
+        <v>9</v>
+      </c>
+      <c r="G27" s="9">
+        <v>10</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C28" s="5">
+        <v>25</v>
+      </c>
+      <c r="D28" s="5">
+        <v>13</v>
+      </c>
+      <c r="E28" s="5">
+        <v>12.7</v>
+      </c>
+      <c r="F28" s="9">
+        <v>9</v>
+      </c>
+      <c r="G28" s="9">
+        <v>10</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="C18" s="12">
+      <c r="B29" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C29" s="5">
+        <v>25</v>
+      </c>
+      <c r="D29" s="5">
+        <v>10</v>
+      </c>
+      <c r="E29" s="5">
         <v>12</v>
       </c>
-      <c r="D18" s="12">
-        <v>30</v>
-      </c>
-      <c r="E18" s="12">
-        <v>10.5</v>
-      </c>
-      <c r="F18" s="9">
-        <v>9</v>
-      </c>
-      <c r="G18" s="9">
-        <v>9</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C19" s="12">
-        <v>10</v>
-      </c>
-      <c r="D19" s="12">
-        <v>15</v>
-      </c>
-      <c r="E19" s="12">
-        <v>7</v>
-      </c>
-      <c r="F19" s="9">
-        <v>9</v>
-      </c>
-      <c r="G19" s="9">
-        <v>10</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C20" s="5">
-        <v>25</v>
-      </c>
-      <c r="D20" s="5">
-        <v>13</v>
-      </c>
-      <c r="E20" s="5">
-        <v>12.7</v>
-      </c>
-      <c r="F20" s="9">
-        <v>9</v>
-      </c>
-      <c r="G20" s="9">
-        <v>10</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
+      <c r="F29" s="9">
+        <v>8</v>
+      </c>
+      <c r="G29" s="9">
+        <v>12</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9207,45 +9881,45 @@
   <sheetData>
     <row r="5" spans="4:19" x14ac:dyDescent="0.2">
       <c r="F5" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="G5" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="J5" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="M5" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="4:19" x14ac:dyDescent="0.2">
       <c r="F6" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="G6" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="H6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="I6" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="J6" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="K6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="L6" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="M6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="N6" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -9253,7 +9927,7 @@
     </row>
     <row r="7" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
@@ -9340,7 +10014,7 @@
     </row>
     <row r="10" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
@@ -9431,7 +10105,7 @@
     </row>
     <row r="12" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="F12">
         <v>-0.1</v>
@@ -9467,7 +10141,7 @@
     </row>
     <row r="13" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="F13">
         <v>-15</v>

--- a/dev_docs/Tetra数值公式_26_4_4.xlsx
+++ b/dev_docs/Tetra数值公式_26_4_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F8F068-7C98-4D1D-ADA0-701B89F0C54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948226D9-A183-4B57-B77F-0DE4FA3CB42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="350">
   <si>
     <t>刀刃</t>
   </si>
@@ -1266,6 +1266,127 @@
   </si>
   <si>
     <t>仇恨-30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.3.2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'cataclysm:witherite_ingot'</t>
+  </si>
+  <si>
+    <t>凋零合金锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>击退抗性+0.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法抗性+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.2.2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'cataclysm:ancient_metal_ingot'</t>
+  </si>
+  <si>
+    <t>!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远古金属</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.2.3</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'cataclysm:ignitium_ingot'</t>
+  </si>
+  <si>
+    <t>腾炎锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法穿透+1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发狂抵抗+0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>癫火抵抗+0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰伤害+4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1443,7 +1564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1517,6 +1638,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1794,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X154"/>
+  <dimension ref="A1:X157"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="8.625" style="3" customWidth="1"/>
@@ -2214,7 +2341,7 @@
       </c>
       <c r="N11" s="11">
         <f>I11*$M$3</f>
-        <v>1.2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="O11" s="9">
         <v>1</v>
@@ -2252,7 +2379,7 @@
       </c>
       <c r="J12" s="17">
         <f t="shared" ref="J12" si="4">(G12*$I$2)+(H12*$I$3)</f>
-        <v>3.45</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="K12" s="9">
         <f t="shared" ref="K12" si="5">(G12*$I$5)+(H12*$I$6)+(I12*$I$7)</f>
@@ -2316,11 +2443,11 @@
       </c>
       <c r="M13" s="11">
         <f t="shared" ref="M13:M26" si="10">I13*$M$2</f>
-        <v>6.875</v>
+        <v>6.8750000000000009</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" ref="N13:N26" si="11">I13*$M$3</f>
-        <v>1.65</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="O13" s="9">
         <v>1</v>
@@ -2380,7 +2507,7 @@
       </c>
       <c r="N14" s="11">
         <f t="shared" si="11"/>
-        <v>1.8</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="O14" s="9">
         <v>1</v>
@@ -2434,7 +2561,7 @@
       </c>
       <c r="N15" s="11">
         <f t="shared" si="11"/>
-        <v>1.8</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="O15" s="9">
         <v>1</v>
@@ -2494,7 +2621,7 @@
       </c>
       <c r="N16" s="11">
         <f t="shared" si="11"/>
-        <v>1.95</v>
+        <v>1.9500000000000002</v>
       </c>
       <c r="O16" s="9">
         <v>1</v>
@@ -2532,7 +2659,7 @@
       </c>
       <c r="J17" s="17">
         <f t="shared" si="9"/>
-        <v>5.7</v>
+        <v>5.6999999999999993</v>
       </c>
       <c r="K17" s="9">
         <f t="shared" si="2"/>
@@ -2540,7 +2667,7 @@
       </c>
       <c r="L17" s="10">
         <f t="shared" si="3"/>
-        <v>7.95</v>
+        <v>7.9499999999999993</v>
       </c>
       <c r="M17" s="11">
         <f t="shared" si="10"/>
@@ -2548,7 +2675,7 @@
       </c>
       <c r="N17" s="11">
         <f t="shared" si="11"/>
-        <v>2.1</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="O17" s="9">
         <v>1</v>
@@ -2608,7 +2735,7 @@
       </c>
       <c r="N18" s="11">
         <f t="shared" si="11"/>
-        <v>2.4</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="O18" s="9">
         <v>1</v>
@@ -2650,15 +2777,15 @@
       </c>
       <c r="J19" s="17">
         <f t="shared" si="9"/>
-        <v>2.0499999999999998</v>
+        <v>2.0500000000000003</v>
       </c>
       <c r="K19" s="9">
         <f t="shared" si="2"/>
-        <v>0.85</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="L19" s="10">
         <f t="shared" si="3"/>
-        <v>2.9</v>
+        <v>2.9000000000000004</v>
       </c>
       <c r="M19" s="11">
         <f t="shared" si="10"/>
@@ -2666,7 +2793,7 @@
       </c>
       <c r="N19" s="11">
         <f t="shared" si="11"/>
-        <v>1.2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="O19" s="9">
         <v>1</v>
@@ -2760,7 +2887,7 @@
       </c>
       <c r="J21" s="17">
         <f t="shared" si="9"/>
-        <v>3.9</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="K21" s="9">
         <f t="shared" si="2"/>
@@ -2776,7 +2903,7 @@
       </c>
       <c r="N21" s="11">
         <f t="shared" si="11"/>
-        <v>1.8</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="O21" s="9">
         <v>1</v>
@@ -2880,7 +3007,7 @@
       </c>
       <c r="N23" s="11">
         <f t="shared" si="11"/>
-        <v>1.2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="O23" s="9">
         <v>1</v>
@@ -2988,11 +3115,11 @@
       </c>
       <c r="M25" s="11">
         <f t="shared" si="10"/>
-        <v>6.875</v>
+        <v>6.8750000000000009</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="11"/>
-        <v>1.65</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="O25" s="9">
         <v>1</v>
@@ -3044,7 +3171,7 @@
       </c>
       <c r="N26" s="11">
         <f t="shared" si="11"/>
-        <v>1.8</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="O26" s="9">
         <v>1</v>
@@ -3102,7 +3229,7 @@
       </c>
       <c r="N27" s="11">
         <f t="shared" ref="N27:N55" si="13">I27*$M$3</f>
-        <v>1.8</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="O27" s="9">
         <v>1</v>
@@ -3154,7 +3281,7 @@
       </c>
       <c r="N28" s="11">
         <f t="shared" si="13"/>
-        <v>1.95</v>
+        <v>1.9500000000000002</v>
       </c>
       <c r="O28" s="9">
         <v>1</v>
@@ -3190,7 +3317,7 @@
       </c>
       <c r="J29" s="17">
         <f t="shared" si="9"/>
-        <v>5.7</v>
+        <v>5.6999999999999993</v>
       </c>
       <c r="K29" s="9">
         <f t="shared" si="2"/>
@@ -3198,7 +3325,7 @@
       </c>
       <c r="L29" s="10">
         <f t="shared" si="3"/>
-        <v>7.95</v>
+        <v>7.9499999999999993</v>
       </c>
       <c r="M29" s="11">
         <f t="shared" si="12"/>
@@ -3206,7 +3333,7 @@
       </c>
       <c r="N29" s="11">
         <f t="shared" si="13"/>
-        <v>2.1</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="O29" s="9">
         <v>2</v>
@@ -3316,7 +3443,7 @@
       </c>
       <c r="N31" s="11">
         <f t="shared" si="13"/>
-        <v>2.4</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="O31" s="9">
         <v>2</v>
@@ -3360,7 +3487,7 @@
       </c>
       <c r="J32" s="17">
         <f t="shared" si="9"/>
-        <v>5.7</v>
+        <v>5.6999999999999993</v>
       </c>
       <c r="K32" s="9">
         <f t="shared" si="2"/>
@@ -3368,7 +3495,7 @@
       </c>
       <c r="L32" s="10">
         <f t="shared" si="3"/>
-        <v>7.95</v>
+        <v>7.9499999999999993</v>
       </c>
       <c r="M32" s="11">
         <f t="shared" si="12"/>
@@ -3430,7 +3557,7 @@
       </c>
       <c r="N33" s="11">
         <f t="shared" si="13"/>
-        <v>2.85</v>
+        <v>2.8499999999999996</v>
       </c>
       <c r="O33" s="9">
         <v>2</v>
@@ -3468,7 +3595,7 @@
       </c>
       <c r="J34" s="17">
         <f t="shared" si="9"/>
-        <v>5.55</v>
+        <v>5.5500000000000007</v>
       </c>
       <c r="K34" s="9">
         <f t="shared" si="2"/>
@@ -3476,7 +3603,7 @@
       </c>
       <c r="L34" s="10">
         <f t="shared" si="3"/>
-        <v>7.8</v>
+        <v>7.8000000000000007</v>
       </c>
       <c r="M34" s="11">
         <f t="shared" si="12"/>
@@ -3598,7 +3725,7 @@
       </c>
       <c r="N36" s="11">
         <f t="shared" si="13"/>
-        <v>2.85</v>
+        <v>2.8499999999999996</v>
       </c>
       <c r="O36" s="9">
         <v>2</v>
@@ -3754,11 +3881,11 @@
       </c>
       <c r="K39" s="9">
         <f t="shared" si="2"/>
-        <v>2.85</v>
+        <v>2.8499999999999996</v>
       </c>
       <c r="L39" s="10">
         <f t="shared" si="3"/>
-        <v>9.9</v>
+        <v>9.8999999999999986</v>
       </c>
       <c r="M39" s="11">
         <f t="shared" si="12"/>
@@ -3820,7 +3947,7 @@
       </c>
       <c r="N40" s="11">
         <f t="shared" ref="N40" si="18">I40*$M$3</f>
-        <v>3.15</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="O40" s="9">
         <v>4</v>
@@ -3918,7 +4045,7 @@
       </c>
       <c r="J42" s="17">
         <f t="shared" si="14"/>
-        <v>7.85</v>
+        <v>7.8500000000000005</v>
       </c>
       <c r="K42" s="9">
         <f t="shared" si="2"/>
@@ -3934,7 +4061,7 @@
       </c>
       <c r="N42" s="11">
         <f t="shared" si="13"/>
-        <v>3.15</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="O42" s="9">
         <v>4</v>
@@ -3990,11 +4117,11 @@
       </c>
       <c r="M43" s="11">
         <f t="shared" si="12"/>
-        <v>13.75</v>
+        <v>13.750000000000002</v>
       </c>
       <c r="N43" s="11">
         <f t="shared" si="13"/>
-        <v>3.3</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O43" s="9">
         <v>4</v>
@@ -4044,11 +4171,11 @@
       </c>
       <c r="M44" s="11">
         <f t="shared" si="12"/>
-        <v>13.75</v>
+        <v>13.750000000000002</v>
       </c>
       <c r="N44" s="11">
         <f t="shared" si="13"/>
-        <v>3.3</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O44" s="9">
         <v>4</v>
@@ -4098,11 +4225,11 @@
       </c>
       <c r="M45" s="11">
         <f t="shared" si="12"/>
-        <v>13.75</v>
+        <v>13.750000000000002</v>
       </c>
       <c r="N45" s="11">
         <f t="shared" si="13"/>
-        <v>3.3</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O45" s="9">
         <v>4</v>
@@ -4152,11 +4279,11 @@
       </c>
       <c r="M46" s="11">
         <f t="shared" ref="M46" si="22">I46*$M$2</f>
-        <v>14.375</v>
+        <v>14.374999999999998</v>
       </c>
       <c r="N46" s="11">
         <f t="shared" ref="N46" si="23">I46*$M$3</f>
-        <v>3.45</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="O46" s="9">
         <v>4</v>
@@ -4212,11 +4339,11 @@
       </c>
       <c r="M47" s="11">
         <f t="shared" si="12"/>
-        <v>14.375</v>
+        <v>14.374999999999998</v>
       </c>
       <c r="N47" s="11">
         <f t="shared" si="13"/>
-        <v>3.45</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="O47" s="9">
         <v>3</v>
@@ -4270,7 +4397,7 @@
       </c>
       <c r="N48" s="11">
         <f t="shared" si="13"/>
-        <v>3.6</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="O48" s="9">
         <v>2</v>
@@ -4284,7 +4411,7 @@
       <c r="R48" s="9"/>
       <c r="S48" s="9"/>
     </row>
-    <row r="49" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>16</v>
       </c>
@@ -4318,11 +4445,11 @@
       </c>
       <c r="K49" s="9">
         <f t="shared" si="2"/>
-        <v>4.2</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="L49" s="10">
         <f t="shared" si="3"/>
-        <v>14.55</v>
+        <v>14.549999999999999</v>
       </c>
       <c r="M49" s="11">
         <f t="shared" si="12"/>
@@ -4346,7 +4473,7 @@
       </c>
       <c r="S49" s="9"/>
     </row>
-    <row r="50" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C50" s="5" t="s">
         <v>154</v>
       </c>
@@ -4402,7 +4529,7 @@
       </c>
       <c r="S50" s="9"/>
     </row>
-    <row r="51" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="5" t="s">
         <v>154</v>
       </c>
@@ -4456,7 +4583,7 @@
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
     </row>
-    <row r="52" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="5" t="s">
         <v>154</v>
       </c>
@@ -4510,7 +4637,7 @@
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
     </row>
-    <row r="53" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>19</v>
       </c>
@@ -4552,11 +4679,11 @@
       </c>
       <c r="M53" s="11">
         <f t="shared" si="12"/>
-        <v>13.75</v>
+        <v>13.750000000000002</v>
       </c>
       <c r="N53" s="11">
         <f t="shared" si="13"/>
-        <v>3.3</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O53" s="9">
         <v>4</v>
@@ -4570,7 +4697,7 @@
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
     </row>
-    <row r="54" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="12" t="s">
         <v>168</v>
       </c>
@@ -4610,7 +4737,7 @@
       </c>
       <c r="N54" s="11">
         <f t="shared" si="13"/>
-        <v>3.9</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="O54" s="9">
         <v>4</v>
@@ -4624,7 +4751,7 @@
       <c r="R54" s="9"/>
       <c r="S54" s="9"/>
     </row>
-    <row r="55" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="12" t="s">
         <v>168</v>
       </c>
@@ -4660,11 +4787,11 @@
       </c>
       <c r="M55" s="11">
         <f t="shared" si="12"/>
-        <v>13.75</v>
+        <v>13.750000000000002</v>
       </c>
       <c r="N55" s="11">
         <f t="shared" si="13"/>
-        <v>3.3</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O55" s="9">
         <v>4</v>
@@ -4680,7 +4807,7 @@
       </c>
       <c r="S55" s="9"/>
     </row>
-    <row r="56" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="5" t="s">
         <v>178</v>
       </c>
@@ -4720,7 +4847,7 @@
       </c>
       <c r="N56" s="11">
         <f t="shared" ref="N56:N57" si="26">I56*$M$3</f>
-        <v>4.2</v>
+        <v>4.1999999999999993</v>
       </c>
       <c r="O56" s="9">
         <v>3</v>
@@ -4734,7 +4861,7 @@
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
     </row>
-    <row r="57" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="5" t="s">
         <v>178</v>
       </c>
@@ -4790,7 +4917,7 @@
       </c>
       <c r="S57" s="9"/>
     </row>
-    <row r="58" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>22</v>
       </c>
@@ -4819,24 +4946,24 @@
         <v>3.2</v>
       </c>
       <c r="J58" s="17">
-        <f t="shared" ref="J58:J63" si="27">(G58*$I$2)+(H58*$I$3)</f>
+        <f t="shared" ref="J58:J64" si="27">(G58*$I$2)+(H58*$I$3)</f>
         <v>15.6</v>
       </c>
       <c r="K58" s="9">
-        <f t="shared" ref="K58:K63" si="28">(G58*$I$5)+(H58*$I$6)+(I58*$I$7)</f>
+        <f t="shared" ref="K58:K64" si="28">(G58*$I$5)+(H58*$I$6)+(I58*$I$7)</f>
         <v>6.15</v>
       </c>
       <c r="L58" s="10">
-        <f t="shared" ref="L58:L63" si="29">J58+K58</f>
+        <f t="shared" ref="L58:L64" si="29">J58+K58</f>
         <v>21.75</v>
       </c>
       <c r="M58" s="11">
-        <f t="shared" ref="M58:M63" si="30">I58*$M$2</f>
+        <f t="shared" ref="M58:M64" si="30">I58*$M$2</f>
         <v>20</v>
       </c>
       <c r="N58" s="11">
-        <f t="shared" ref="N58:N63" si="31">I58*$M$3</f>
-        <v>4.8</v>
+        <f t="shared" ref="N58:N64" si="31">I58*$M$3</f>
+        <v>4.8000000000000007</v>
       </c>
       <c r="O58" s="9">
         <v>4</v>
@@ -4852,7 +4979,7 @@
       </c>
       <c r="S58" s="9"/>
     </row>
-    <row r="59" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>14</v>
       </c>
@@ -4898,7 +5025,7 @@
       </c>
       <c r="N59" s="11">
         <f t="shared" si="31"/>
-        <v>3.6</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="O59" s="9">
         <v>2</v>
@@ -4912,7 +5039,7 @@
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
     </row>
-    <row r="60" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="5" t="s">
         <v>192</v>
       </c>
@@ -4968,7 +5095,7 @@
       </c>
       <c r="S60" s="9"/>
     </row>
-    <row r="61" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>24</v>
       </c>
@@ -5014,7 +5141,7 @@
       </c>
       <c r="N61" s="11">
         <f t="shared" si="31"/>
-        <v>4.95</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="O61" s="9">
         <v>2</v>
@@ -5028,113 +5155,112 @@
       <c r="R61" s="9"/>
       <c r="S61" s="9"/>
     </row>
-    <row r="62" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
-        <v>24</v>
-      </c>
-      <c r="B62" s="3">
-        <v>20</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G62" s="12">
+    <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="F62" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="G62" s="5">
         <v>7</v>
       </c>
-      <c r="H62" s="12">
-        <v>6</v>
-      </c>
-      <c r="I62" s="12">
-        <v>3.2</v>
+      <c r="H62" s="5">
+        <v>8</v>
+      </c>
+      <c r="I62" s="5">
+        <v>2.9</v>
       </c>
       <c r="J62" s="17">
         <f t="shared" si="27"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K62" s="9">
         <f t="shared" si="28"/>
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="L62" s="10">
         <f t="shared" si="29"/>
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
       <c r="M62" s="11">
         <f t="shared" si="30"/>
-        <v>20</v>
+        <v>18.125</v>
       </c>
       <c r="N62" s="11">
         <f t="shared" si="31"/>
-        <v>4.8</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="O62" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P62" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="R62" s="9"/>
+        <v>4</v>
+      </c>
+      <c r="Q62" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="R62" s="23" t="s">
+        <v>338</v>
+      </c>
       <c r="S62" s="9"/>
-    </row>
-    <row r="63" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U62" s="24" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B63" s="3">
-        <v>30</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G63" s="5">
-        <v>8</v>
-      </c>
-      <c r="H63" s="5">
+      <c r="G63" s="12">
+        <v>7</v>
+      </c>
+      <c r="H63" s="12">
         <v>6</v>
       </c>
-      <c r="I63" s="5">
-        <v>3.5</v>
+      <c r="I63" s="12">
+        <v>3.2</v>
       </c>
       <c r="J63" s="17">
         <f t="shared" si="27"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K63" s="9">
         <f t="shared" si="28"/>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="L63" s="10">
         <f t="shared" si="29"/>
-        <v>26</v>
+        <v>23.5</v>
       </c>
       <c r="M63" s="11">
         <f t="shared" si="30"/>
-        <v>21.875</v>
+        <v>20</v>
       </c>
       <c r="N63" s="11">
         <f t="shared" si="31"/>
-        <v>5.25</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="O63" s="9">
         <v>3</v>
@@ -5142,62 +5268,68 @@
       <c r="P63" s="9">
         <v>3</v>
       </c>
-      <c r="Q63" s="24" t="s">
-        <v>300</v>
+      <c r="Q63" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
     </row>
-    <row r="64" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
+        <v>29</v>
+      </c>
+      <c r="B64" s="3">
+        <v>30</v>
+      </c>
       <c r="C64" s="5" t="s">
         <v>203</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G64" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H64" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I64" s="5">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J64" s="17">
-        <f t="shared" ref="J64:J70" si="32">(G64*$I$2)+(H64*$I$3)</f>
-        <v>20</v>
+        <f t="shared" si="27"/>
+        <v>19</v>
       </c>
       <c r="K64" s="9">
-        <f t="shared" ref="K64:K70" si="33">(G64*$I$5)+(H64*$I$6)+(I64*$I$7)</f>
-        <v>6.5</v>
+        <f t="shared" si="28"/>
+        <v>7</v>
       </c>
       <c r="L64" s="10">
-        <f t="shared" ref="L64:L70" si="34">J64+K64</f>
-        <v>26.5</v>
+        <f t="shared" si="29"/>
+        <v>26</v>
       </c>
       <c r="M64" s="11">
-        <f t="shared" ref="M64:M70" si="35">I64*$M$2</f>
-        <v>25</v>
+        <f t="shared" si="30"/>
+        <v>21.875</v>
       </c>
       <c r="N64" s="11">
-        <f t="shared" ref="N64:N70" si="36">I64*$M$3</f>
-        <v>6</v>
+        <f t="shared" si="31"/>
+        <v>5.25</v>
       </c>
       <c r="O64" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P64" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q64" s="23" t="s">
-        <v>299</v>
+        <v>3</v>
+      </c>
+      <c r="Q64" s="24" t="s">
+        <v>300</v>
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
@@ -5207,51 +5339,51 @@
         <v>203</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G65" s="5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H65" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I65" s="5">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J65" s="17">
-        <f t="shared" si="32"/>
-        <v>22.7</v>
+        <f t="shared" ref="J65:J71" si="32">(G65*$I$2)+(H65*$I$3)</f>
+        <v>20</v>
       </c>
       <c r="K65" s="9">
-        <f t="shared" si="33"/>
-        <v>8.3000000000000007</v>
+        <f t="shared" ref="K65:K71" si="33">(G65*$I$5)+(H65*$I$6)+(I65*$I$7)</f>
+        <v>6.5</v>
       </c>
       <c r="L65" s="10">
-        <f t="shared" si="34"/>
-        <v>31</v>
+        <f t="shared" ref="L65:L71" si="34">J65+K65</f>
+        <v>26.5</v>
       </c>
       <c r="M65" s="11">
-        <f t="shared" si="35"/>
-        <v>30</v>
+        <f t="shared" ref="M65:M71" si="35">I65*$M$2</f>
+        <v>25</v>
       </c>
       <c r="N65" s="11">
-        <f t="shared" si="36"/>
-        <v>7.2</v>
+        <f t="shared" ref="N65:N71" si="36">I65*$M$3</f>
+        <v>6</v>
       </c>
       <c r="O65" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P65" s="9">
         <v>4</v>
       </c>
-      <c r="Q65" s="9" t="s">
-        <v>210</v>
+      <c r="Q65" s="23" t="s">
+        <v>299</v>
       </c>
       <c r="R65" s="9"/>
       <c r="S65" s="9"/>
@@ -5261,42 +5393,42 @@
         <v>203</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G66" s="5">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="H66" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I66" s="5">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J66" s="17">
         <f t="shared" si="32"/>
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="K66" s="9">
         <f t="shared" si="33"/>
-        <v>10</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="L66" s="10">
         <f t="shared" si="34"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M66" s="11">
         <f t="shared" si="35"/>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N66" s="11">
         <f t="shared" si="36"/>
-        <v>6</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="O66" s="9">
         <v>5</v>
@@ -5305,112 +5437,112 @@
         <v>4</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="R66" s="9"/>
       <c r="S66" s="9"/>
     </row>
     <row r="67" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
-        <v>35</v>
-      </c>
-      <c r="B67" s="3">
-        <v>40</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="F67" s="12" t="s">
+      <c r="C67" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G67" s="12">
-        <v>9</v>
-      </c>
-      <c r="H67" s="12">
+      <c r="G67" s="5">
+        <v>8</v>
+      </c>
+      <c r="H67" s="5">
         <v>12</v>
       </c>
-      <c r="I67" s="12">
-        <v>6</v>
+      <c r="I67" s="5">
+        <v>4</v>
       </c>
       <c r="J67" s="17">
         <f t="shared" si="32"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K67" s="9">
         <f t="shared" si="33"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L67" s="10">
         <f t="shared" si="34"/>
-        <v>34.5</v>
+        <v>32</v>
       </c>
       <c r="M67" s="11">
         <f t="shared" si="35"/>
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="N67" s="11">
         <f t="shared" si="36"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O67" s="9">
+        <v>5</v>
+      </c>
+      <c r="P67" s="9">
         <v>4</v>
       </c>
-      <c r="P67" s="9">
-        <v>5</v>
-      </c>
       <c r="Q67" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="R67" s="9"/>
       <c r="S67" s="9"/>
     </row>
     <row r="68" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <v>35</v>
+      </c>
+      <c r="B68" s="3">
+        <v>40</v>
+      </c>
       <c r="C68" s="12" t="s">
         <v>214</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G68" s="12">
+        <v>9</v>
+      </c>
+      <c r="H68" s="12">
         <v>12</v>
       </c>
-      <c r="H68" s="12">
-        <v>5</v>
-      </c>
       <c r="I68" s="12">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="J68" s="17">
         <f t="shared" si="32"/>
-        <v>26.5</v>
+        <v>24</v>
       </c>
       <c r="K68" s="9">
         <f t="shared" si="33"/>
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L68" s="10">
         <f t="shared" si="34"/>
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="M68" s="11">
         <f t="shared" si="35"/>
-        <v>40.625</v>
+        <v>37.5</v>
       </c>
       <c r="N68" s="11">
         <f t="shared" si="36"/>
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="O68" s="9">
         <v>4</v>
@@ -5419,656 +5551,654 @@
         <v>5</v>
       </c>
       <c r="Q68" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="R68" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="S68" s="9" t="s">
-        <v>220</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="R68" s="9"/>
+      <c r="S68" s="9"/>
     </row>
     <row r="69" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C69" s="12" t="s">
         <v>214</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G69" s="12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H69" s="12">
         <v>5</v>
       </c>
       <c r="I69" s="12">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J69" s="17">
         <f t="shared" si="32"/>
-        <v>22.5</v>
+        <v>26.5</v>
       </c>
       <c r="K69" s="9">
         <f t="shared" si="33"/>
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="L69" s="10">
         <f t="shared" si="34"/>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M69" s="11">
         <f t="shared" si="35"/>
-        <v>37.5</v>
+        <v>40.625</v>
       </c>
       <c r="N69" s="11">
         <f t="shared" si="36"/>
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="O69" s="9">
         <v>4</v>
       </c>
       <c r="P69" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q69" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="R69" s="9"/>
-      <c r="S69" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="Q69" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="R69" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="S69" s="9" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="70" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C70" s="12" t="s">
         <v>214</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G70" s="12">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H70" s="12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I70" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J70" s="17">
         <f t="shared" si="32"/>
-        <v>40</v>
+        <v>22.5</v>
       </c>
       <c r="K70" s="9">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="L70" s="10">
         <f t="shared" si="34"/>
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="M70" s="11">
         <f t="shared" si="35"/>
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="N70" s="11">
         <f t="shared" si="36"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O70" s="9">
         <v>4</v>
       </c>
       <c r="P70" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q70" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="R70" s="9"/>
+      <c r="S70" s="9"/>
+    </row>
+    <row r="71" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C71" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" s="12">
+        <v>18</v>
+      </c>
+      <c r="H71" s="12">
+        <v>8</v>
+      </c>
+      <c r="I71" s="12">
+        <v>8</v>
+      </c>
+      <c r="J71" s="17">
+        <f t="shared" si="32"/>
+        <v>40</v>
+      </c>
+      <c r="K71" s="9">
+        <f t="shared" si="33"/>
+        <v>13</v>
+      </c>
+      <c r="L71" s="10">
+        <f t="shared" si="34"/>
+        <v>53</v>
+      </c>
+      <c r="M71" s="11">
+        <f t="shared" si="35"/>
+        <v>50</v>
+      </c>
+      <c r="N71" s="11">
+        <f t="shared" si="36"/>
+        <v>12</v>
+      </c>
+      <c r="O71" s="9">
+        <v>4</v>
+      </c>
+      <c r="P71" s="9">
         <v>6</v>
       </c>
-      <c r="Q70" s="23" t="s">
+      <c r="Q71" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="R70" s="23" t="s">
+      <c r="R71" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="S70" s="23" t="s">
+      <c r="S71" s="23" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
+    <row r="72" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
         <v>40</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B72" s="3">
         <v>45</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G71" s="5">
-        <v>14</v>
-      </c>
-      <c r="H71" s="5">
-        <v>6</v>
-      </c>
-      <c r="I71" s="5">
-        <v>7</v>
-      </c>
-      <c r="J71" s="17">
-        <f t="shared" ref="J71:J76" si="37">(G71*$I$2)+(H71*$I$3)</f>
-        <v>31</v>
-      </c>
-      <c r="K71" s="9">
-        <f t="shared" ref="K71:K76" si="38">(G71*$I$5)+(H71*$I$6)+(I71*$I$7)</f>
-        <v>10</v>
-      </c>
-      <c r="L71" s="10">
-        <f t="shared" ref="L71:L76" si="39">J71+K71</f>
-        <v>41</v>
-      </c>
-      <c r="M71" s="11">
-        <f t="shared" ref="M71:M76" si="40">I71*$M$2</f>
-        <v>43.75</v>
-      </c>
-      <c r="N71" s="11">
-        <f t="shared" ref="N71:N76" si="41">I71*$M$3</f>
-        <v>10.5</v>
-      </c>
-      <c r="O71" s="9">
-        <v>6</v>
-      </c>
-      <c r="P71" s="9">
-        <v>5</v>
-      </c>
-      <c r="Q71" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="R71" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="S71" s="9"/>
-    </row>
-    <row r="72" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C72" s="5" t="s">
         <v>225</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G72" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H72" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I72" s="5">
         <v>7</v>
       </c>
       <c r="J72" s="17">
+        <f t="shared" ref="J72:J77" si="37">(G72*$I$2)+(H72*$I$3)</f>
+        <v>31</v>
+      </c>
+      <c r="K72" s="9">
+        <f t="shared" ref="K72:K77" si="38">(G72*$I$5)+(H72*$I$6)+(I72*$I$7)</f>
+        <v>10</v>
+      </c>
+      <c r="L72" s="10">
+        <f t="shared" ref="L72:L77" si="39">J72+K72</f>
+        <v>41</v>
+      </c>
+      <c r="M72" s="11">
+        <f t="shared" ref="M72:M77" si="40">I72*$M$2</f>
+        <v>43.75</v>
+      </c>
+      <c r="N72" s="11">
+        <f t="shared" ref="N72:N77" si="41">I72*$M$3</f>
+        <v>10.5</v>
+      </c>
+      <c r="O72" s="9">
+        <v>6</v>
+      </c>
+      <c r="P72" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="R72" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="S72" s="9"/>
+    </row>
+    <row r="73" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C73" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" s="5">
+        <v>17</v>
+      </c>
+      <c r="H73" s="5">
+        <v>2</v>
+      </c>
+      <c r="I73" s="5">
+        <v>7</v>
+      </c>
+      <c r="J73" s="17">
         <f t="shared" si="37"/>
         <v>35</v>
       </c>
-      <c r="K72" s="9">
+      <c r="K73" s="9">
         <f t="shared" si="38"/>
         <v>9.5</v>
       </c>
-      <c r="L72" s="10">
+      <c r="L73" s="10">
         <f t="shared" si="39"/>
         <v>44.5</v>
       </c>
-      <c r="M72" s="11">
+      <c r="M73" s="11">
         <f t="shared" si="40"/>
         <v>43.75</v>
       </c>
-      <c r="N72" s="11">
+      <c r="N73" s="11">
         <f t="shared" si="41"/>
         <v>10.5</v>
       </c>
-      <c r="O72" s="9">
+      <c r="O73" s="9">
         <v>6</v>
       </c>
-      <c r="P72" s="9">
+      <c r="P73" s="9">
         <v>6</v>
       </c>
-      <c r="Q72" s="9" t="s">
+      <c r="Q73" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="R72" s="9" t="s">
+      <c r="R73" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="S72" s="9"/>
-    </row>
-    <row r="73" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
+      <c r="S73" s="9"/>
+    </row>
+    <row r="74" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
         <v>45</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B74" s="3">
         <v>50</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C74" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D74" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="E73" s="12" t="s">
+      <c r="E74" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="F74" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G73" s="12">
+      <c r="G74" s="12">
         <v>15.5</v>
       </c>
-      <c r="H73" s="12">
+      <c r="H74" s="12">
         <v>6</v>
       </c>
-      <c r="I73" s="12">
+      <c r="I74" s="12">
         <v>8</v>
       </c>
-      <c r="J73" s="17">
+      <c r="J74" s="17">
         <f t="shared" si="37"/>
         <v>34</v>
       </c>
-      <c r="K73" s="9">
+      <c r="K74" s="9">
         <f t="shared" si="38"/>
         <v>10.75</v>
       </c>
-      <c r="L73" s="10">
+      <c r="L74" s="10">
         <f t="shared" si="39"/>
         <v>44.75</v>
       </c>
-      <c r="M73" s="11">
+      <c r="M74" s="11">
         <f t="shared" si="40"/>
         <v>50</v>
       </c>
-      <c r="N73" s="11">
+      <c r="N74" s="11">
         <f t="shared" si="41"/>
         <v>12</v>
       </c>
-      <c r="O73" s="9">
+      <c r="O74" s="9">
         <v>6</v>
       </c>
-      <c r="P73" s="9">
+      <c r="P74" s="9">
         <v>6</v>
       </c>
-      <c r="Q73" s="9" t="s">
+      <c r="Q74" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="R73" s="9" t="s">
+      <c r="R74" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="S73" s="9"/>
-    </row>
-    <row r="74" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="12" t="s">
+      <c r="S74" s="9"/>
+    </row>
+    <row r="75" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C75" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D75" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="E74" s="12" t="s">
+      <c r="E75" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="F75" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G74" s="12">
+      <c r="G75" s="12">
         <v>13</v>
       </c>
-      <c r="H74" s="12">
+      <c r="H75" s="12">
         <v>5</v>
       </c>
-      <c r="I74" s="12">
+      <c r="I75" s="12">
         <v>7</v>
       </c>
-      <c r="J74" s="17">
+      <c r="J75" s="17">
         <f t="shared" si="37"/>
         <v>28.5</v>
       </c>
-      <c r="K74" s="9">
+      <c r="K75" s="9">
         <f t="shared" si="38"/>
         <v>9</v>
       </c>
-      <c r="L74" s="10">
+      <c r="L75" s="10">
         <f t="shared" si="39"/>
         <v>37.5</v>
       </c>
-      <c r="M74" s="11">
+      <c r="M75" s="11">
         <f t="shared" si="40"/>
         <v>43.75</v>
       </c>
-      <c r="N74" s="11">
+      <c r="N75" s="11">
         <f t="shared" si="41"/>
         <v>10.5</v>
       </c>
-      <c r="O74" s="9">
+      <c r="O75" s="9">
         <v>5</v>
       </c>
-      <c r="P74" s="9">
+      <c r="P75" s="9">
         <v>5</v>
       </c>
-      <c r="Q74" s="23" t="s">
+      <c r="Q75" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="R74" s="23" t="s">
+      <c r="R75" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="S74" s="9"/>
-    </row>
-    <row r="75" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
+      <c r="S75" s="9"/>
+    </row>
+    <row r="76" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
         <v>40</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B76" s="3">
         <v>45</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C76" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D76" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E76" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F76" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G75" s="5">
+      <c r="G76" s="5">
         <v>14</v>
       </c>
-      <c r="H75" s="5">
+      <c r="H76" s="5">
         <v>5</v>
       </c>
-      <c r="I75" s="5">
+      <c r="I76" s="5">
         <v>7.5</v>
       </c>
-      <c r="J75" s="17">
+      <c r="J76" s="17">
         <f t="shared" si="37"/>
         <v>30.5</v>
       </c>
-      <c r="K75" s="9">
+      <c r="K76" s="9">
         <f t="shared" si="38"/>
         <v>9.5</v>
       </c>
-      <c r="L75" s="10">
+      <c r="L76" s="10">
         <f t="shared" si="39"/>
         <v>40</v>
       </c>
-      <c r="M75" s="11">
+      <c r="M76" s="11">
         <f t="shared" si="40"/>
         <v>46.875</v>
       </c>
-      <c r="N75" s="11">
+      <c r="N76" s="11">
         <f t="shared" si="41"/>
         <v>11.25</v>
       </c>
-      <c r="O75" s="9">
+      <c r="O76" s="9">
         <v>6</v>
       </c>
-      <c r="P75" s="9">
+      <c r="P76" s="9">
         <v>7</v>
       </c>
-      <c r="Q75" s="23" t="s">
+      <c r="Q76" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="R75" s="23" t="s">
+      <c r="R76" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="S75" s="9"/>
-    </row>
-    <row r="76" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
+      <c r="S76" s="9"/>
+    </row>
+    <row r="77" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
         <v>50</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B77" s="3">
         <v>60</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C77" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D77" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="E77" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="F76" s="12" t="s">
+      <c r="F77" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G76" s="12">
+      <c r="G77" s="12">
         <v>15</v>
       </c>
-      <c r="H76" s="12">
+      <c r="H77" s="12">
         <v>7</v>
       </c>
-      <c r="I76" s="12">
+      <c r="I77" s="12">
         <v>9.5</v>
       </c>
-      <c r="J76" s="17">
+      <c r="J77" s="17">
         <f t="shared" si="37"/>
         <v>33.5</v>
       </c>
-      <c r="K76" s="9">
+      <c r="K77" s="9">
         <f t="shared" si="38"/>
         <v>11</v>
       </c>
-      <c r="L76" s="10">
+      <c r="L77" s="10">
         <f t="shared" si="39"/>
         <v>44.5</v>
       </c>
-      <c r="M76" s="11">
+      <c r="M77" s="11">
         <f t="shared" si="40"/>
         <v>59.375</v>
       </c>
-      <c r="N76" s="11">
+      <c r="N77" s="11">
         <f t="shared" si="41"/>
         <v>14.25</v>
       </c>
-      <c r="O76" s="9">
-        <v>7</v>
-      </c>
-      <c r="P76" s="9">
-        <v>7</v>
-      </c>
-      <c r="Q76" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="R76" s="9"/>
-      <c r="S76" s="9"/>
-    </row>
-    <row r="77" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C77" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G77" s="12">
-        <v>16</v>
-      </c>
-      <c r="H77" s="12">
-        <v>10</v>
-      </c>
-      <c r="I77" s="12">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="J77" s="17">
-        <f t="shared" ref="J77:J86" si="42">(G77*$I$2)+(H77*$I$3)</f>
-        <v>37</v>
-      </c>
-      <c r="K77" s="9">
-        <f t="shared" ref="K77:K86" si="43">(G77*$I$5)+(H77*$I$6)+(I77*$I$7)</f>
-        <v>13</v>
-      </c>
-      <c r="L77" s="10">
-        <f t="shared" ref="L77:L86" si="44">J77+K77</f>
-        <v>50</v>
-      </c>
-      <c r="M77" s="11">
-        <f t="shared" ref="M77:M86" si="45">I77*$M$2</f>
-        <v>61.25</v>
-      </c>
-      <c r="N77" s="11">
-        <f t="shared" ref="N77:N86" si="46">I77*$M$3</f>
-        <v>14.7</v>
-      </c>
       <c r="O77" s="9">
         <v>7</v>
       </c>
       <c r="P77" s="9">
         <v>7</v>
       </c>
-      <c r="Q77" s="23" t="s">
+      <c r="Q77" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="R77" s="9"/>
+      <c r="S77" s="9"/>
+    </row>
+    <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C78" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G78" s="12">
+        <v>16</v>
+      </c>
+      <c r="H78" s="12">
+        <v>10</v>
+      </c>
+      <c r="I78" s="12">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J78" s="17">
+        <f t="shared" ref="J78:J89" si="42">(G78*$I$2)+(H78*$I$3)</f>
+        <v>37</v>
+      </c>
+      <c r="K78" s="9">
+        <f t="shared" ref="K78:K89" si="43">(G78*$I$5)+(H78*$I$6)+(I78*$I$7)</f>
+        <v>13</v>
+      </c>
+      <c r="L78" s="10">
+        <f t="shared" ref="L78:L89" si="44">J78+K78</f>
+        <v>50</v>
+      </c>
+      <c r="M78" s="11">
+        <f t="shared" ref="M78:M89" si="45">I78*$M$2</f>
+        <v>61.250000000000007</v>
+      </c>
+      <c r="N78" s="11">
+        <f t="shared" ref="N78:N89" si="46">I78*$M$3</f>
+        <v>14.700000000000001</v>
+      </c>
+      <c r="O78" s="9">
+        <v>7</v>
+      </c>
+      <c r="P78" s="9">
+        <v>7</v>
+      </c>
+      <c r="Q78" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="R77" s="23" t="s">
+      <c r="R78" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="S77" s="9"/>
-    </row>
-    <row r="78" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
+      <c r="S78" s="9"/>
+    </row>
+    <row r="79" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
         <v>60</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B79" s="3">
         <v>65</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C79" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="D79" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E79" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F79" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G78" s="5">
+      <c r="G79" s="5">
         <v>20</v>
       </c>
-      <c r="H78" s="5">
+      <c r="H79" s="5">
         <v>10</v>
       </c>
-      <c r="I78" s="5">
+      <c r="I79" s="5">
         <v>10</v>
       </c>
-      <c r="J78" s="17">
+      <c r="J79" s="17">
         <f t="shared" si="42"/>
         <v>45</v>
       </c>
-      <c r="K78" s="9">
+      <c r="K79" s="9">
         <f t="shared" si="43"/>
         <v>15</v>
       </c>
-      <c r="L78" s="10">
+      <c r="L79" s="10">
         <f t="shared" si="44"/>
         <v>60</v>
       </c>
-      <c r="M78" s="11">
+      <c r="M79" s="11">
         <f t="shared" si="45"/>
         <v>62.5</v>
       </c>
-      <c r="N78" s="11">
+      <c r="N79" s="11">
         <f t="shared" si="46"/>
         <v>15</v>
       </c>
-      <c r="O78" s="9">
-        <v>8</v>
-      </c>
-      <c r="P78" s="9">
-        <v>8</v>
-      </c>
-      <c r="Q78" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="R78" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="S78" s="9"/>
-    </row>
-    <row r="79" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C79" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G79" s="5">
-        <v>23</v>
-      </c>
-      <c r="H79" s="5">
-        <v>8</v>
-      </c>
-      <c r="I79" s="5">
-        <v>11</v>
-      </c>
-      <c r="J79" s="17">
-        <f t="shared" si="42"/>
-        <v>50</v>
-      </c>
-      <c r="K79" s="9">
-        <f t="shared" si="43"/>
-        <v>15.5</v>
-      </c>
-      <c r="L79" s="10">
-        <f t="shared" si="44"/>
-        <v>65.5</v>
-      </c>
-      <c r="M79" s="11">
-        <f t="shared" si="45"/>
-        <v>68.75</v>
-      </c>
-      <c r="N79" s="11">
-        <f t="shared" si="46"/>
-        <v>16.5</v>
-      </c>
       <c r="O79" s="9">
         <v>8</v>
       </c>
       <c r="P79" s="9">
         <v>8</v>
       </c>
-      <c r="Q79" s="23" t="s">
-        <v>309</v>
+      <c r="Q79" s="9" t="s">
+        <v>248</v>
       </c>
       <c r="R79" s="9" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="S79" s="9"/>
     </row>
@@ -6077,42 +6207,42 @@
         <v>245</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G80" s="5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H80" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I80" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J80" s="17">
         <f t="shared" si="42"/>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K80" s="9">
         <f t="shared" si="43"/>
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="L80" s="10">
         <f t="shared" si="44"/>
-        <v>60.5</v>
+        <v>65.5</v>
       </c>
       <c r="M80" s="11">
         <f t="shared" si="45"/>
-        <v>62.5</v>
+        <v>68.75</v>
       </c>
       <c r="N80" s="11">
         <f t="shared" si="46"/>
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="O80" s="9">
         <v>8</v>
@@ -6121,298 +6251,291 @@
         <v>8</v>
       </c>
       <c r="Q80" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="R80" s="23" t="s">
-        <v>310</v>
+        <v>309</v>
+      </c>
+      <c r="R80" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="S80" s="9"/>
     </row>
-    <row r="81" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
-        <v>70</v>
-      </c>
-      <c r="B81" s="3">
-        <v>70</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F81" s="12" t="s">
+    <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C81" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G81" s="12">
-        <v>25</v>
-      </c>
-      <c r="H81" s="12">
-        <v>9</v>
-      </c>
-      <c r="I81" s="12">
-        <v>11.5</v>
+      <c r="G81" s="5">
+        <v>17</v>
+      </c>
+      <c r="H81" s="5">
+        <v>18</v>
+      </c>
+      <c r="I81" s="5">
+        <v>10</v>
       </c>
       <c r="J81" s="17">
         <f t="shared" si="42"/>
-        <v>54.5</v>
+        <v>43</v>
       </c>
       <c r="K81" s="9">
         <f t="shared" si="43"/>
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="L81" s="10">
         <f t="shared" si="44"/>
-        <v>71.5</v>
+        <v>60.5</v>
       </c>
       <c r="M81" s="11">
         <f t="shared" si="45"/>
-        <v>71.875</v>
+        <v>62.5</v>
       </c>
       <c r="N81" s="11">
         <f t="shared" si="46"/>
-        <v>17.25</v>
+        <v>15</v>
       </c>
       <c r="O81" s="9">
         <v>8</v>
       </c>
       <c r="P81" s="9">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="R81" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="S81" s="9"/>
+    </row>
+    <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C82" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="E82" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="F82" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="G82" s="5">
+        <v>15</v>
+      </c>
+      <c r="H82" s="5">
+        <v>20</v>
+      </c>
+      <c r="I82" s="5">
         <v>9</v>
-      </c>
-      <c r="Q81" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="R81" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="S81" s="23" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C82" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G82" s="12">
-        <v>25</v>
-      </c>
-      <c r="H82" s="12">
-        <v>8</v>
-      </c>
-      <c r="I82" s="12">
-        <v>11.6</v>
       </c>
       <c r="J82" s="17">
         <f t="shared" si="42"/>
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="K82" s="9">
         <f t="shared" si="43"/>
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="L82" s="10">
         <f t="shared" si="44"/>
-        <v>70.5</v>
+        <v>57.5</v>
       </c>
       <c r="M82" s="11">
         <f t="shared" si="45"/>
-        <v>72.5</v>
+        <v>56.25</v>
       </c>
       <c r="N82" s="11">
         <f t="shared" si="46"/>
-        <v>17.399999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="O82" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P82" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q82" s="23" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="R82" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="S82" s="9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+      <c r="S82" s="9"/>
+      <c r="U82" s="24" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <v>70</v>
+      </c>
+      <c r="B83" s="3">
+        <v>70</v>
+      </c>
       <c r="C83" s="12" t="s">
         <v>254</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G83" s="12">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H83" s="12">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I83" s="12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J83" s="17">
         <f t="shared" si="42"/>
-        <v>51.5</v>
+        <v>54.5</v>
       </c>
       <c r="K83" s="9">
         <f t="shared" si="43"/>
-        <v>21.5</v>
+        <v>17</v>
       </c>
       <c r="L83" s="10">
         <f t="shared" si="44"/>
-        <v>73</v>
+        <v>71.5</v>
       </c>
       <c r="M83" s="11">
         <f t="shared" si="45"/>
-        <v>68.75</v>
+        <v>71.875</v>
       </c>
       <c r="N83" s="11">
         <f t="shared" si="46"/>
-        <v>16.5</v>
+        <v>17.25</v>
       </c>
       <c r="O83" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P83" s="9">
-        <v>6</v>
-      </c>
-      <c r="Q83" s="23" t="s">
-        <v>316</v>
+        <v>9</v>
+      </c>
+      <c r="Q83" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="R83" s="23" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="S83" s="23" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
-        <v>80</v>
-      </c>
-      <c r="B84" s="3">
-        <v>75</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D84" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="F84" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C84" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F84" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G84" s="5">
-        <v>27</v>
-      </c>
-      <c r="H84" s="5">
-        <v>14</v>
-      </c>
-      <c r="I84" s="5">
-        <v>12</v>
+      <c r="G84" s="12">
+        <v>25</v>
+      </c>
+      <c r="H84" s="12">
+        <v>8</v>
+      </c>
+      <c r="I84" s="12">
+        <v>11.6</v>
       </c>
       <c r="J84" s="17">
         <f t="shared" si="42"/>
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="K84" s="9">
         <f t="shared" si="43"/>
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="L84" s="10">
         <f t="shared" si="44"/>
-        <v>81.5</v>
+        <v>70.5</v>
       </c>
       <c r="M84" s="11">
         <f t="shared" si="45"/>
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="N84" s="11">
         <f t="shared" si="46"/>
-        <v>18</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="O84" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P84" s="9">
         <v>9</v>
       </c>
-      <c r="Q84" s="9" t="s">
-        <v>265</v>
+      <c r="Q84" s="23" t="s">
+        <v>314</v>
       </c>
       <c r="R84" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="S84" s="23" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="F85" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="S84" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C85" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F85" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G85" s="5">
+      <c r="G85" s="12">
+        <v>20</v>
+      </c>
+      <c r="H85" s="12">
+        <v>23</v>
+      </c>
+      <c r="I85" s="12">
         <v>11</v>
-      </c>
-      <c r="H85" s="5">
-        <v>28</v>
-      </c>
-      <c r="I85" s="5">
-        <v>10</v>
       </c>
       <c r="J85" s="17">
         <f t="shared" si="42"/>
-        <v>36</v>
+        <v>51.5</v>
       </c>
       <c r="K85" s="9">
         <f t="shared" si="43"/>
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="L85" s="10">
         <f t="shared" si="44"/>
-        <v>55.5</v>
+        <v>73</v>
       </c>
       <c r="M85" s="11">
         <f t="shared" si="45"/>
-        <v>62.5</v>
+        <v>68.75</v>
       </c>
       <c r="N85" s="11">
         <f t="shared" si="46"/>
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="O85" s="9">
         <v>6</v>
@@ -6421,54 +6544,56 @@
         <v>6</v>
       </c>
       <c r="Q85" s="23" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="R85" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="S85" s="9"/>
-    </row>
-    <row r="86" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C86" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G86" s="5">
+        <v>318</v>
+      </c>
+      <c r="S85" s="23" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C86" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="E86" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="F86" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="G86" s="12">
+        <v>21</v>
+      </c>
+      <c r="H86" s="12">
+        <v>20</v>
+      </c>
+      <c r="I86" s="12">
         <v>10</v>
-      </c>
-      <c r="H86" s="5">
-        <v>35</v>
-      </c>
-      <c r="I86" s="5">
-        <v>10.5</v>
       </c>
       <c r="J86" s="17">
         <f t="shared" si="42"/>
-        <v>37.5</v>
+        <v>52</v>
       </c>
       <c r="K86" s="9">
         <f t="shared" si="43"/>
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="L86" s="10">
         <f t="shared" si="44"/>
-        <v>60</v>
+        <v>72.5</v>
       </c>
       <c r="M86" s="11">
         <f t="shared" si="45"/>
-        <v>65.625</v>
+        <v>62.5</v>
       </c>
       <c r="N86" s="11">
         <f t="shared" si="46"/>
-        <v>15.75</v>
+        <v>15</v>
       </c>
       <c r="O86" s="9">
         <v>6</v>
@@ -6477,367 +6602,436 @@
         <v>8</v>
       </c>
       <c r="Q86" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="R86" s="9"/>
-      <c r="S86" s="9"/>
-    </row>
-    <row r="87" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+      <c r="R86" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="S86" s="23"/>
+      <c r="U86" s="24" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B87" s="3">
-        <v>65</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="F87" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D87" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G87" s="12">
+      <c r="G87" s="5">
+        <v>27</v>
+      </c>
+      <c r="H87" s="5">
+        <v>14</v>
+      </c>
+      <c r="I87" s="5">
         <v>12</v>
       </c>
-      <c r="H87" s="12">
-        <v>30</v>
-      </c>
-      <c r="I87" s="12">
-        <v>10.5</v>
-      </c>
       <c r="J87" s="17">
-        <f t="shared" ref="J87:J97" si="47">(G87*$I$2)+(H87*$I$3)</f>
-        <v>39</v>
+        <f t="shared" si="42"/>
+        <v>61</v>
       </c>
       <c r="K87" s="9">
-        <f t="shared" ref="K87:K109" si="48">(G87*$I$5)+(H87*$I$6)+(I87*$I$7)</f>
-        <v>21</v>
+        <f t="shared" si="43"/>
+        <v>20.5</v>
       </c>
       <c r="L87" s="10">
-        <f t="shared" ref="L87:L97" si="49">J87+K87</f>
-        <v>60</v>
+        <f t="shared" si="44"/>
+        <v>81.5</v>
       </c>
       <c r="M87" s="11">
-        <f t="shared" ref="M87:M110" si="50">I87*$M$2</f>
-        <v>65.625</v>
+        <f t="shared" si="45"/>
+        <v>75</v>
       </c>
       <c r="N87" s="11">
-        <f t="shared" ref="N87:N110" si="51">I87*$M$3</f>
-        <v>15.75</v>
+        <f t="shared" si="46"/>
+        <v>18</v>
       </c>
       <c r="O87" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P87" s="9">
         <v>9</v>
       </c>
-      <c r="Q87" s="23" t="s">
+      <c r="Q87" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="R87" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="S87" s="23" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C88" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G88" s="5">
+        <v>11</v>
+      </c>
+      <c r="H88" s="5">
+        <v>28</v>
+      </c>
+      <c r="I88" s="5">
+        <v>10</v>
+      </c>
+      <c r="J88" s="17">
+        <f t="shared" si="42"/>
+        <v>36</v>
+      </c>
+      <c r="K88" s="9">
+        <f t="shared" si="43"/>
+        <v>19.5</v>
+      </c>
+      <c r="L88" s="10">
+        <f t="shared" si="44"/>
+        <v>55.5</v>
+      </c>
+      <c r="M88" s="11">
+        <f t="shared" si="45"/>
+        <v>62.5</v>
+      </c>
+      <c r="N88" s="11">
+        <f t="shared" si="46"/>
+        <v>15</v>
+      </c>
+      <c r="O88" s="9">
+        <v>6</v>
+      </c>
+      <c r="P88" s="9">
+        <v>6</v>
+      </c>
+      <c r="Q88" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="R88" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="S88" s="9"/>
+    </row>
+    <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C89" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G89" s="5">
+        <v>10</v>
+      </c>
+      <c r="H89" s="5">
+        <v>35</v>
+      </c>
+      <c r="I89" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="J89" s="17">
+        <f t="shared" si="42"/>
+        <v>37.5</v>
+      </c>
+      <c r="K89" s="9">
+        <f t="shared" si="43"/>
+        <v>22.5</v>
+      </c>
+      <c r="L89" s="10">
+        <f t="shared" si="44"/>
+        <v>60</v>
+      </c>
+      <c r="M89" s="11">
+        <f t="shared" si="45"/>
+        <v>65.625</v>
+      </c>
+      <c r="N89" s="11">
+        <f t="shared" si="46"/>
+        <v>15.75</v>
+      </c>
+      <c r="O89" s="9">
+        <v>6</v>
+      </c>
+      <c r="P89" s="9">
+        <v>8</v>
+      </c>
+      <c r="Q89" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="R89" s="9"/>
+      <c r="S89" s="9"/>
+    </row>
+    <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="3">
+        <v>60</v>
+      </c>
+      <c r="B90" s="3">
+        <v>65</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G90" s="12">
+        <v>12</v>
+      </c>
+      <c r="H90" s="12">
+        <v>30</v>
+      </c>
+      <c r="I90" s="12">
+        <v>10.5</v>
+      </c>
+      <c r="J90" s="17">
+        <f t="shared" ref="J90:J100" si="47">(G90*$I$2)+(H90*$I$3)</f>
+        <v>39</v>
+      </c>
+      <c r="K90" s="9">
+        <f t="shared" ref="K90:K112" si="48">(G90*$I$5)+(H90*$I$6)+(I90*$I$7)</f>
+        <v>21</v>
+      </c>
+      <c r="L90" s="10">
+        <f t="shared" ref="L90:L100" si="49">J90+K90</f>
+        <v>60</v>
+      </c>
+      <c r="M90" s="11">
+        <f t="shared" ref="M90:M113" si="50">I90*$M$2</f>
+        <v>65.625</v>
+      </c>
+      <c r="N90" s="11">
+        <f t="shared" ref="N90:N113" si="51">I90*$M$3</f>
+        <v>15.75</v>
+      </c>
+      <c r="O90" s="9">
+        <v>9</v>
+      </c>
+      <c r="P90" s="9">
+        <v>9</v>
+      </c>
+      <c r="Q90" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="R87" s="9"/>
-      <c r="S87" s="9"/>
-    </row>
-    <row r="88" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C88" s="12" t="s">
+      <c r="R90" s="9"/>
+      <c r="S90" s="9"/>
+    </row>
+    <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C91" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D88" s="21" t="s">
+      <c r="D91" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="E88" s="12" t="s">
+      <c r="E91" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="F88" s="12" t="s">
+      <c r="F91" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G88" s="12">
+      <c r="G91" s="12">
         <v>10</v>
       </c>
-      <c r="H88" s="12">
+      <c r="H91" s="12">
         <v>15</v>
       </c>
-      <c r="I88" s="12">
+      <c r="I91" s="12">
         <v>7</v>
       </c>
-      <c r="J88" s="17">
+      <c r="J91" s="17">
         <f t="shared" si="47"/>
         <v>27.5</v>
       </c>
-      <c r="K88" s="9">
+      <c r="K91" s="9">
         <f t="shared" si="48"/>
         <v>12.5</v>
       </c>
-      <c r="L88" s="10">
+      <c r="L91" s="10">
         <f t="shared" si="49"/>
         <v>40</v>
       </c>
-      <c r="M88" s="11">
+      <c r="M91" s="11">
         <f t="shared" si="50"/>
         <v>43.75</v>
       </c>
-      <c r="N88" s="11">
+      <c r="N91" s="11">
         <f t="shared" si="51"/>
         <v>10.5</v>
       </c>
-      <c r="O88" s="9">
+      <c r="O91" s="9">
         <v>9</v>
       </c>
-      <c r="P88" s="9">
+      <c r="P91" s="9">
         <v>10</v>
       </c>
-      <c r="Q88" s="23" t="s">
+      <c r="Q91" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="R88" s="9"/>
-      <c r="S88" s="9"/>
-    </row>
-    <row r="89" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
+      <c r="R91" s="9"/>
+      <c r="S91" s="9"/>
+    </row>
+    <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="3">
         <v>75</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B92" s="3">
         <v>80</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C92" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D92" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E92" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F92" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G89" s="5">
+      <c r="G92" s="5">
         <v>25</v>
       </c>
-      <c r="H89" s="5">
+      <c r="H92" s="5">
         <v>13</v>
       </c>
-      <c r="I89" s="5">
+      <c r="I92" s="5">
         <v>12.7</v>
       </c>
-      <c r="J89" s="17">
+      <c r="J92" s="17">
         <f t="shared" si="47"/>
         <v>56.5</v>
       </c>
-      <c r="K89" s="9">
+      <c r="K92" s="9">
         <f t="shared" si="48"/>
         <v>19</v>
       </c>
-      <c r="L89" s="10">
+      <c r="L92" s="10">
         <f t="shared" si="49"/>
         <v>75.5</v>
       </c>
-      <c r="M89" s="11">
+      <c r="M92" s="11">
         <f t="shared" si="50"/>
         <v>79.375</v>
       </c>
-      <c r="N89" s="11">
+      <c r="N92" s="11">
         <f t="shared" si="51"/>
-        <v>19.05</v>
-      </c>
-      <c r="O89" s="9">
+        <v>19.049999999999997</v>
+      </c>
+      <c r="O92" s="9">
         <v>9</v>
       </c>
-      <c r="P89" s="9">
+      <c r="P92" s="9">
         <v>10</v>
       </c>
-      <c r="Q89" s="3" t="s">
+      <c r="Q92" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="R89" s="23" t="s">
+      <c r="R92" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="S89" s="9" t="s">
+      <c r="S92" s="9" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C90" s="5" t="s">
+    <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C93" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D93" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E93" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F93" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G90" s="5">
+      <c r="G93" s="5">
         <v>25</v>
       </c>
-      <c r="H90" s="5">
+      <c r="H93" s="5">
         <v>10</v>
       </c>
-      <c r="I90" s="5">
+      <c r="I93" s="5">
         <v>12</v>
       </c>
-      <c r="J90" s="17">
+      <c r="J93" s="17">
         <f t="shared" si="47"/>
         <v>55</v>
       </c>
-      <c r="K90" s="9">
+      <c r="K93" s="9">
         <f t="shared" si="48"/>
         <v>17.5</v>
       </c>
-      <c r="L90" s="10">
+      <c r="L93" s="10">
         <f t="shared" si="49"/>
         <v>72.5</v>
       </c>
-      <c r="M90" s="11">
+      <c r="M93" s="11">
         <f t="shared" si="50"/>
         <v>75</v>
       </c>
-      <c r="N90" s="11">
+      <c r="N93" s="11">
         <f t="shared" si="51"/>
         <v>18</v>
       </c>
-      <c r="O90" s="9">
+      <c r="O93" s="9">
         <v>8</v>
       </c>
-      <c r="P90" s="9">
+      <c r="P93" s="9">
         <v>12</v>
       </c>
-      <c r="Q90" s="9" t="s">
+      <c r="Q93" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="R90" s="23" t="s">
+      <c r="R93" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="S90" s="23" t="s">
+      <c r="S93" s="23" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
+    <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="3">
         <v>77</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B94" s="3">
         <v>85</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C94" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="9"/>
-      <c r="J91" s="17">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="K91" s="9">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="L91" s="10">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="11">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="N91" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="O91" s="9"/>
-      <c r="P91" s="9"/>
-      <c r="Q91" s="9"/>
-      <c r="R91" s="9"/>
-      <c r="S91" s="9"/>
-    </row>
-    <row r="92" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="9"/>
-      <c r="J92" s="17">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="9">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="L92" s="10">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="11">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="N92" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="O92" s="9"/>
-      <c r="P92" s="9"/>
-      <c r="Q92" s="9"/>
-      <c r="R92" s="9"/>
-      <c r="S92" s="9"/>
-    </row>
-    <row r="93" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
-        <v>80</v>
-      </c>
-      <c r="B93" s="3">
-        <v>90</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="17">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="K93" s="9">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="L93" s="10">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="M93" s="11">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="N93" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="O93" s="9"/>
-      <c r="P93" s="9"/>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-    </row>
-    <row r="94" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
@@ -6870,7 +7064,7 @@
       <c r="R94" s="9"/>
       <c r="S94" s="9"/>
     </row>
-    <row r="95" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
@@ -6904,8 +7098,16 @@
       <c r="R95" s="9"/>
       <c r="S95" s="9"/>
     </row>
-    <row r="96" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C96" s="9"/>
+    <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="3">
+        <v>80</v>
+      </c>
+      <c r="B96" s="3">
+        <v>90</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
@@ -6981,7 +7183,7 @@
       <c r="H98" s="9"/>
       <c r="I98" s="9"/>
       <c r="J98" s="17">
-        <f t="shared" ref="J98:J118" si="52">(G98*$I$2)+(H98*$I$3)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K98" s="9">
@@ -6989,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L98" s="10">
-        <f t="shared" ref="L98:L118" si="53">J98+K98</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M98" s="11">
@@ -7015,7 +7217,7 @@
       <c r="H99" s="9"/>
       <c r="I99" s="9"/>
       <c r="J99" s="17">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K99" s="9">
@@ -7023,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="L99" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M99" s="11">
@@ -7049,7 +7251,7 @@
       <c r="H100" s="9"/>
       <c r="I100" s="9"/>
       <c r="J100" s="17">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K100" s="9">
@@ -7057,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="L100" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M100" s="11">
@@ -7083,7 +7285,7 @@
       <c r="H101" s="9"/>
       <c r="I101" s="9"/>
       <c r="J101" s="17">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="J101:J121" si="52">(G101*$I$2)+(H101*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K101" s="9">
@@ -7091,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="L101" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="L101:L121" si="53">J101+K101</f>
         <v>0</v>
       </c>
       <c r="M101" s="11">
@@ -7393,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="9">
-        <f t="shared" ref="K110:K154" si="54">(G110*$I$5)+(H110*$I$6)+(I110*$I$7)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L110" s="10">
@@ -7427,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L111" s="10">
@@ -7435,11 +7637,11 @@
         <v>0</v>
       </c>
       <c r="M111" s="11">
-        <f t="shared" ref="M111:M154" si="55">I111*$M$2</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="N111" s="11">
-        <f t="shared" ref="N111:N154" si="56">I111*$M$3</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="O111" s="9"/>
@@ -7461,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L112" s="10">
@@ -7469,11 +7671,11 @@
         <v>0</v>
       </c>
       <c r="M112" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="N112" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="O112" s="9"/>
@@ -7495,7 +7697,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="K113:K157" si="54">(G113*$I$5)+(H113*$I$6)+(I113*$I$7)</f>
         <v>0</v>
       </c>
       <c r="L113" s="10">
@@ -7503,11 +7705,11 @@
         <v>0</v>
       </c>
       <c r="M113" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="N113" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="O113" s="9"/>
@@ -7537,11 +7739,11 @@
         <v>0</v>
       </c>
       <c r="M114" s="11">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="M114:M157" si="55">I114*$M$2</f>
         <v>0</v>
       </c>
       <c r="N114" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="N114:N157" si="56">I114*$M$3</f>
         <v>0</v>
       </c>
       <c r="O114" s="9"/>
@@ -7695,7 +7897,7 @@
       <c r="H119" s="9"/>
       <c r="I119" s="9"/>
       <c r="J119" s="17">
-        <f t="shared" ref="J119:J154" si="57">(G119*$I$2)+(H119*$I$3)</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K119" s="9">
@@ -7703,7 +7905,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="10">
-        <f t="shared" ref="L119:L154" si="58">J119+K119</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="M119" s="11">
@@ -7729,7 +7931,7 @@
       <c r="H120" s="9"/>
       <c r="I120" s="9"/>
       <c r="J120" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K120" s="9">
@@ -7737,7 +7939,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="M120" s="11">
@@ -7763,7 +7965,7 @@
       <c r="H121" s="9"/>
       <c r="I121" s="9"/>
       <c r="J121" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K121" s="9">
@@ -7771,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="M121" s="11">
@@ -7797,7 +7999,7 @@
       <c r="H122" s="9"/>
       <c r="I122" s="9"/>
       <c r="J122" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="J122:J157" si="57">(G122*$I$2)+(H122*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K122" s="9">
@@ -7805,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="L122:L157" si="58">J122+K122</f>
         <v>0</v>
       </c>
       <c r="M122" s="11">
@@ -8909,6 +9111,108 @@
       <c r="Q154" s="9"/>
       <c r="R154" s="9"/>
       <c r="S154" s="9"/>
+    </row>
+    <row r="155" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C155" s="9"/>
+      <c r="D155" s="9"/>
+      <c r="E155" s="9"/>
+      <c r="F155" s="9"/>
+      <c r="G155" s="9"/>
+      <c r="H155" s="9"/>
+      <c r="I155" s="9"/>
+      <c r="J155" s="17">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="K155" s="9">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L155" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M155" s="11">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N155" s="11">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="O155" s="9"/>
+      <c r="P155" s="9"/>
+      <c r="Q155" s="9"/>
+      <c r="R155" s="9"/>
+      <c r="S155" s="9"/>
+    </row>
+    <row r="156" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C156" s="9"/>
+      <c r="D156" s="9"/>
+      <c r="E156" s="9"/>
+      <c r="F156" s="9"/>
+      <c r="G156" s="9"/>
+      <c r="H156" s="9"/>
+      <c r="I156" s="9"/>
+      <c r="J156" s="17">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="K156" s="9">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L156" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M156" s="11">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N156" s="11">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="O156" s="9"/>
+      <c r="P156" s="9"/>
+      <c r="Q156" s="9"/>
+      <c r="R156" s="9"/>
+      <c r="S156" s="9"/>
+    </row>
+    <row r="157" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C157" s="9"/>
+      <c r="D157" s="9"/>
+      <c r="E157" s="9"/>
+      <c r="F157" s="9"/>
+      <c r="G157" s="9"/>
+      <c r="H157" s="9"/>
+      <c r="I157" s="9"/>
+      <c r="J157" s="17">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="K157" s="9">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L157" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M157" s="11">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N157" s="11">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="O157" s="9"/>
+      <c r="P157" s="9"/>
+      <c r="Q157" s="9"/>
+      <c r="R157" s="9"/>
+      <c r="S157" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/dev_docs/Tetra数值公式_26_4_4.xlsx
+++ b/dev_docs/Tetra数值公式_26_4_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948226D9-A183-4B57-B77F-0DE4FA3CB42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A040ED1A-181A-4704-9354-E8DB1E7D516F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="350">
   <si>
     <t>刀刃</t>
   </si>
@@ -1133,33 +1133,6 @@
         <color theme="1"/>
         <rFont val="等线"/>
         <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>仇恨-0.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1378,15 +1351,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>发狂抵抗+0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>癫火抵抗+0.05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>火焰伤害+4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>发狂抵抗+5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1634,16 +1611,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1969,10 +1946,10 @@
       <c r="S1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="25" t="s">
+      <c r="U1" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="V1" s="25"/>
+      <c r="V1" s="27"/>
     </row>
     <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
@@ -2019,12 +1996,12 @@
       <c r="S2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="U2" s="25" t="s">
+      <c r="U2" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
     </row>
     <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="3" t="s">
@@ -2068,12 +2045,12 @@
       <c r="S3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="25" t="s">
+      <c r="U3" s="27" t="s">
         <v>298</v>
       </c>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
     </row>
     <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
@@ -2292,7 +2269,7 @@
         <v>49</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5156,17 +5133,17 @@
       <c r="S61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C62" s="27" t="s">
+      <c r="C62" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="25" t="s">
         <v>333</v>
       </c>
-      <c r="E62" s="27" t="s">
+      <c r="F62" s="25" t="s">
         <v>334</v>
-      </c>
-      <c r="F62" s="27" t="s">
-        <v>335</v>
       </c>
       <c r="G62" s="5">
         <v>7</v>
@@ -5204,14 +5181,14 @@
         <v>4</v>
       </c>
       <c r="Q62" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="R62" s="23" t="s">
         <v>337</v>
-      </c>
-      <c r="R62" s="23" t="s">
-        <v>338</v>
       </c>
       <c r="S62" s="9"/>
       <c r="U62" s="24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6133,7 +6110,7 @@
         <v>7</v>
       </c>
       <c r="Q78" s="23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="R78" s="23" t="s">
         <v>303</v>
@@ -6315,17 +6292,17 @@
       <c r="S81" s="9"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C82" s="27" t="s">
+      <c r="C82" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="D82" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="D82" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="E82" s="27" t="s">
-        <v>342</v>
-      </c>
-      <c r="F82" s="27" t="s">
-        <v>335</v>
+      <c r="E82" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="F82" s="25" t="s">
+        <v>334</v>
       </c>
       <c r="G82" s="5">
         <v>15</v>
@@ -6363,14 +6340,14 @@
         <v>8</v>
       </c>
       <c r="Q82" s="23" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="R82" s="23" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="S82" s="9"/>
       <c r="U82" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6554,17 +6531,17 @@
       </c>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C86" s="28" t="s">
+      <c r="C86" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="D86" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="E86" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="E86" s="28" t="s">
-        <v>345</v>
-      </c>
-      <c r="F86" s="28" t="s">
-        <v>335</v>
+      <c r="F86" s="26" t="s">
+        <v>334</v>
       </c>
       <c r="G86" s="12">
         <v>21</v>
@@ -6602,14 +6579,14 @@
         <v>8</v>
       </c>
       <c r="Q86" s="23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R86" s="23" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="S86" s="23"/>
       <c r="U86" s="24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6725,10 +6702,10 @@
         <v>6</v>
       </c>
       <c r="Q88" s="23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R88" s="23" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="S88" s="9"/>
     </row>
@@ -6781,7 +6758,7 @@
         <v>8</v>
       </c>
       <c r="Q89" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R89" s="9"/>
       <c r="S89" s="9"/>
@@ -6841,7 +6818,7 @@
         <v>9</v>
       </c>
       <c r="Q90" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R90" s="9"/>
       <c r="S90" s="9"/>
@@ -6895,7 +6872,7 @@
         <v>10</v>
       </c>
       <c r="Q91" s="23" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R91" s="9"/>
       <c r="S91" s="9"/>
@@ -6958,7 +6935,7 @@
         <v>278</v>
       </c>
       <c r="R92" s="23" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="S92" s="9" t="s">
         <v>279</v>
@@ -7016,10 +6993,10 @@
         <v>151</v>
       </c>
       <c r="R93" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="S93" s="23" t="s">
         <v>328</v>
-      </c>
-      <c r="S93" s="23" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -9268,896 +9245,459 @@
       <c r="J1" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="K1" s="24" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>205</v>
+        <v>332</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>333</v>
       </c>
       <c r="C2" s="5">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5">
         <v>8</v>
       </c>
-      <c r="D2" s="5">
-        <v>6</v>
-      </c>
       <c r="E2" s="5">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="F2" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="9">
-        <v>3</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11"/>
+        <v>4</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11">
+        <v>1</v>
+      </c>
       <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>207</v>
+        <v>339</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>341</v>
       </c>
       <c r="C3" s="5">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5">
         <v>9</v>
       </c>
-      <c r="D3" s="5">
-        <v>4</v>
-      </c>
-      <c r="E3" s="5">
-        <v>4</v>
-      </c>
       <c r="F3" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="11"/>
+        <v>346</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="J3" s="10"/>
+      <c r="K3" s="11">
+        <v>2</v>
+      </c>
       <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="5">
-        <v>9.6</v>
-      </c>
-      <c r="D4" s="5">
-        <v>7</v>
-      </c>
-      <c r="E4" s="5">
-        <v>4.8</v>
+      <c r="A4" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="12">
+        <v>21</v>
+      </c>
+      <c r="D4" s="12">
+        <v>20</v>
+      </c>
+      <c r="E4" s="12">
+        <v>10</v>
       </c>
       <c r="F4" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="9">
-        <v>4</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="11"/>
+        <v>8</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="11">
+        <v>2</v>
+      </c>
       <c r="L4" s="11"/>
     </row>
     <row r="5" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C5" s="5">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5">
-        <v>4</v>
-      </c>
-      <c r="F5" s="9">
-        <v>5</v>
-      </c>
-      <c r="G5" s="9">
-        <v>4</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>213</v>
-      </c>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="12">
-        <v>9</v>
-      </c>
-      <c r="D6" s="12">
-        <v>12</v>
-      </c>
-      <c r="E6" s="12">
-        <v>6</v>
-      </c>
-      <c r="F6" s="9">
-        <v>4</v>
-      </c>
-      <c r="G6" s="9">
-        <v>5</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>217</v>
-      </c>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="C7" s="12">
-        <v>12</v>
-      </c>
-      <c r="D7" s="12">
-        <v>5</v>
-      </c>
-      <c r="E7" s="12">
-        <v>6.5</v>
-      </c>
-      <c r="F7" s="9">
-        <v>4</v>
-      </c>
-      <c r="G7" s="9">
-        <v>5</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>220</v>
-      </c>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="C8" s="12">
-        <v>10</v>
-      </c>
-      <c r="D8" s="12">
-        <v>5</v>
-      </c>
-      <c r="E8" s="12">
-        <v>6</v>
-      </c>
-      <c r="F8" s="9">
-        <v>4</v>
-      </c>
-      <c r="G8" s="9">
-        <v>4</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>301</v>
-      </c>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="23"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="12">
-        <v>18</v>
-      </c>
-      <c r="D9" s="12">
-        <v>8</v>
-      </c>
-      <c r="E9" s="12">
-        <v>8</v>
-      </c>
-      <c r="F9" s="9">
-        <v>4</v>
-      </c>
-      <c r="G9" s="9">
-        <v>6</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>303</v>
-      </c>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C10" s="5">
-        <v>14</v>
-      </c>
-      <c r="D10" s="5">
-        <v>6</v>
-      </c>
-      <c r="E10" s="5">
-        <v>7</v>
-      </c>
-      <c r="F10" s="9">
-        <v>6</v>
-      </c>
-      <c r="G10" s="9">
-        <v>5</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>151</v>
-      </c>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C11" s="5">
-        <v>17</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5">
-        <v>7</v>
-      </c>
-      <c r="F11" s="9">
-        <v>6</v>
-      </c>
-      <c r="G11" s="9">
-        <v>6</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>217</v>
-      </c>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="C12" s="12">
-        <v>15.5</v>
-      </c>
-      <c r="D12" s="12">
-        <v>6</v>
-      </c>
-      <c r="E12" s="12">
-        <v>8</v>
-      </c>
-      <c r="F12" s="9">
-        <v>6</v>
-      </c>
-      <c r="G12" s="9">
-        <v>6</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>199</v>
-      </c>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="9"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="12">
-        <v>13</v>
-      </c>
-      <c r="D13" s="12">
-        <v>5</v>
-      </c>
-      <c r="E13" s="12">
-        <v>7</v>
-      </c>
-      <c r="F13" s="9">
-        <v>5</v>
-      </c>
-      <c r="G13" s="9">
-        <v>5</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>305</v>
-      </c>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
       <c r="J13" s="9"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C14" s="5">
-        <v>14</v>
-      </c>
-      <c r="D14" s="5">
-        <v>5</v>
-      </c>
-      <c r="E14" s="5">
-        <v>7.5</v>
-      </c>
-      <c r="F14" s="9">
-        <v>6</v>
-      </c>
-      <c r="G14" s="9">
-        <v>7</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>308</v>
-      </c>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
       <c r="J14" s="9"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="C15" s="12">
-        <v>15</v>
-      </c>
-      <c r="D15" s="12">
-        <v>7</v>
-      </c>
-      <c r="E15" s="12">
-        <v>9.5</v>
-      </c>
-      <c r="F15" s="9">
-        <v>7</v>
-      </c>
-      <c r="G15" s="9">
-        <v>7</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>243</v>
-      </c>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="C16" s="12">
-        <v>16</v>
-      </c>
-      <c r="D16" s="12">
-        <v>10</v>
-      </c>
-      <c r="E16" s="12">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="F16" s="9">
-        <v>7</v>
-      </c>
-      <c r="G16" s="9">
-        <v>7</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>303</v>
-      </c>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
       <c r="J16" s="9"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C17" s="5">
-        <v>20</v>
-      </c>
-      <c r="D17" s="5">
-        <v>10</v>
-      </c>
-      <c r="E17" s="5">
-        <v>10</v>
-      </c>
-      <c r="F17" s="9">
-        <v>8</v>
-      </c>
-      <c r="G17" s="9">
-        <v>8</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>249</v>
-      </c>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C18" s="5">
-        <v>23</v>
-      </c>
-      <c r="D18" s="5">
-        <v>8</v>
-      </c>
-      <c r="E18" s="5">
-        <v>11</v>
-      </c>
-      <c r="F18" s="9">
-        <v>8</v>
-      </c>
-      <c r="G18" s="9">
-        <v>8</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>108</v>
-      </c>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C19" s="5">
-        <v>17</v>
-      </c>
-      <c r="D19" s="5">
-        <v>18</v>
-      </c>
-      <c r="E19" s="5">
-        <v>10</v>
-      </c>
-      <c r="F19" s="9">
-        <v>8</v>
-      </c>
-      <c r="G19" s="9">
-        <v>8</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>310</v>
-      </c>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
       <c r="J19" s="9"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="C20" s="12">
-        <v>25</v>
-      </c>
-      <c r="D20" s="12">
-        <v>9</v>
-      </c>
-      <c r="E20" s="12">
-        <v>11.5</v>
-      </c>
-      <c r="F20" s="9">
-        <v>8</v>
-      </c>
-      <c r="G20" s="9">
-        <v>9</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="J20" s="23" t="s">
-        <v>312</v>
-      </c>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="C21" s="12">
-        <v>25</v>
-      </c>
-      <c r="D21" s="12">
-        <v>8</v>
-      </c>
-      <c r="E21" s="12">
-        <v>11.6</v>
-      </c>
-      <c r="F21" s="9">
-        <v>7</v>
-      </c>
-      <c r="G21" s="9">
-        <v>9</v>
-      </c>
-      <c r="H21" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>220</v>
-      </c>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="9"/>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="C22" s="12">
-        <v>20</v>
-      </c>
-      <c r="D22" s="12">
-        <v>23</v>
-      </c>
-      <c r="E22" s="12">
-        <v>11</v>
-      </c>
-      <c r="F22" s="9">
-        <v>6</v>
-      </c>
-      <c r="G22" s="9">
-        <v>6</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="J22" s="23" t="s">
-        <v>317</v>
-      </c>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C23" s="5">
-        <v>27</v>
-      </c>
-      <c r="D23" s="5">
-        <v>14</v>
-      </c>
-      <c r="E23" s="5">
-        <v>12</v>
-      </c>
-      <c r="F23" s="9">
-        <v>8</v>
-      </c>
-      <c r="G23" s="9">
-        <v>9</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="J23" s="23" t="s">
-        <v>319</v>
-      </c>
+      <c r="A23" s="22"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="C24" s="5">
-        <v>11</v>
-      </c>
-      <c r="D24" s="5">
-        <v>28</v>
-      </c>
-      <c r="E24" s="5">
-        <v>10</v>
-      </c>
-      <c r="F24" s="9">
-        <v>6</v>
-      </c>
-      <c r="G24" s="9">
-        <v>6</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="I24" s="23" t="s">
-        <v>322</v>
-      </c>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
       <c r="J24" s="9"/>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C25" s="5">
-        <v>10</v>
-      </c>
-      <c r="D25" s="5">
-        <v>35</v>
-      </c>
-      <c r="E25" s="5">
-        <v>10.5</v>
-      </c>
-      <c r="F25" s="9">
-        <v>6</v>
-      </c>
-      <c r="G25" s="9">
-        <v>8</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>324</v>
-      </c>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="23"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="C26" s="12">
-        <v>12</v>
-      </c>
-      <c r="D26" s="12">
-        <v>30</v>
-      </c>
-      <c r="E26" s="12">
-        <v>10.5</v>
-      </c>
-      <c r="F26" s="9">
-        <v>9</v>
-      </c>
-      <c r="G26" s="9">
-        <v>9</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>325</v>
-      </c>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="23"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="C27" s="12">
-        <v>10</v>
-      </c>
-      <c r="D27" s="12">
-        <v>15</v>
-      </c>
-      <c r="E27" s="12">
-        <v>7</v>
-      </c>
-      <c r="F27" s="9">
-        <v>9</v>
-      </c>
-      <c r="G27" s="9">
-        <v>10</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>326</v>
-      </c>
+      <c r="A27" s="21"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="23"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C28" s="5">
-        <v>25</v>
-      </c>
-      <c r="D28" s="5">
-        <v>13</v>
-      </c>
-      <c r="E28" s="5">
-        <v>12.7</v>
-      </c>
-      <c r="F28" s="9">
-        <v>9</v>
-      </c>
-      <c r="G28" s="9">
-        <v>10</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="I28" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>279</v>
-      </c>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="9"/>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C29" s="5">
-        <v>25</v>
-      </c>
-      <c r="D29" s="5">
-        <v>10</v>
-      </c>
-      <c r="E29" s="5">
-        <v>12</v>
-      </c>
-      <c r="F29" s="9">
-        <v>8</v>
-      </c>
-      <c r="G29" s="9">
-        <v>12</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>329</v>
-      </c>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
     </row>

--- a/dev_docs/Tetra数值公式_26_4_4.xlsx
+++ b/dev_docs/Tetra数值公式_26_4_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A040ED1A-181A-4704-9354-E8DB1E7D516F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B519451-0673-494D-96BD-CD7FFBB055F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="345">
   <si>
     <t>刀刃</t>
   </si>
@@ -788,15 +788,6 @@
   </si>
   <si>
     <t>2.2.3</t>
-  </si>
-  <si>
-    <t>kubejs:trinity_alloy_ingot</t>
-  </si>
-  <si>
-    <t>三项合金</t>
-  </si>
-  <si>
-    <t>生命值+3%</t>
   </si>
   <si>
     <t>kubejs:coil_of_sorrow'</t>
@@ -1037,27 +1028,6 @@
       </rPr>
       <t>%</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>冰霜伤害+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火焰伤害+3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1898,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X157"/>
+  <dimension ref="A1:X156"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="8.625" style="3" customWidth="1"/>
@@ -1947,7 +1917,7 @@
         <v>11</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="V1" s="27"/>
     </row>
@@ -1997,7 +1967,7 @@
         <v>15</v>
       </c>
       <c r="U2" s="27" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="V2" s="27"/>
       <c r="W2" s="27"/>
@@ -2046,7 +2016,7 @@
         <v>21</v>
       </c>
       <c r="U3" s="27" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="V3" s="28"/>
       <c r="W3" s="28"/>
@@ -2269,7 +2239,7 @@
         <v>49</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5134,16 +5104,16 @@
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="25" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E62" s="25" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G62" s="5">
         <v>7</v>
@@ -5181,14 +5151,14 @@
         <v>4</v>
       </c>
       <c r="Q62" s="23" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="R62" s="23" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="S62" s="9"/>
       <c r="U62" s="24" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5306,7 +5276,7 @@
         <v>3</v>
       </c>
       <c r="Q64" s="24" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
@@ -5360,7 +5330,7 @@
         <v>4</v>
       </c>
       <c r="Q65" s="23" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="R65" s="9"/>
       <c r="S65" s="9"/>
@@ -5640,7 +5610,7 @@
         <v>4</v>
       </c>
       <c r="Q70" s="23" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="R70" s="9"/>
       <c r="S70" s="9"/>
@@ -5694,13 +5664,13 @@
         <v>6</v>
       </c>
       <c r="Q71" s="23" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="R71" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="S71" s="23" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5932,10 +5902,10 @@
         <v>5</v>
       </c>
       <c r="Q75" s="23" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="R75" s="23" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="S75" s="9"/>
     </row>
@@ -5994,10 +5964,10 @@
         <v>7</v>
       </c>
       <c r="Q76" s="23" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="R76" s="23" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="S76" s="9"/>
     </row>
@@ -6084,23 +6054,23 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J78" s="17">
-        <f t="shared" ref="J78:J89" si="42">(G78*$I$2)+(H78*$I$3)</f>
+        <f t="shared" ref="J78:J88" si="42">(G78*$I$2)+(H78*$I$3)</f>
         <v>37</v>
       </c>
       <c r="K78" s="9">
-        <f t="shared" ref="K78:K89" si="43">(G78*$I$5)+(H78*$I$6)+(I78*$I$7)</f>
+        <f t="shared" ref="K78:K88" si="43">(G78*$I$5)+(H78*$I$6)+(I78*$I$7)</f>
         <v>13</v>
       </c>
       <c r="L78" s="10">
-        <f t="shared" ref="L78:L89" si="44">J78+K78</f>
+        <f t="shared" ref="L78:L88" si="44">J78+K78</f>
         <v>50</v>
       </c>
       <c r="M78" s="11">
-        <f t="shared" ref="M78:M89" si="45">I78*$M$2</f>
+        <f t="shared" ref="M78:M88" si="45">I78*$M$2</f>
         <v>61.250000000000007</v>
       </c>
       <c r="N78" s="11">
-        <f t="shared" ref="N78:N89" si="46">I78*$M$3</f>
+        <f t="shared" ref="N78:N88" si="46">I78*$M$3</f>
         <v>14.700000000000001</v>
       </c>
       <c r="O78" s="9">
@@ -6110,10 +6080,10 @@
         <v>7</v>
       </c>
       <c r="Q78" s="23" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="R78" s="23" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="S78" s="9"/>
     </row>
@@ -6228,7 +6198,7 @@
         <v>8</v>
       </c>
       <c r="Q80" s="23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="R80" s="9" t="s">
         <v>108</v>
@@ -6284,25 +6254,25 @@
         <v>8</v>
       </c>
       <c r="Q81" s="23" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="R81" s="23" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="S81" s="9"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C82" s="25" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E82" s="25" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G82" s="5">
         <v>15</v>
@@ -6340,14 +6310,14 @@
         <v>8</v>
       </c>
       <c r="Q82" s="23" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="R82" s="23" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S82" s="9"/>
       <c r="U82" s="24" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6373,45 +6343,45 @@
         <v>25</v>
       </c>
       <c r="H83" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I83" s="12">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="J83" s="17">
         <f t="shared" si="42"/>
-        <v>54.5</v>
+        <v>54</v>
       </c>
       <c r="K83" s="9">
         <f t="shared" si="43"/>
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="L83" s="10">
         <f t="shared" si="44"/>
-        <v>71.5</v>
+        <v>70.5</v>
       </c>
       <c r="M83" s="11">
         <f t="shared" si="45"/>
-        <v>71.875</v>
+        <v>72.5</v>
       </c>
       <c r="N83" s="11">
         <f t="shared" si="46"/>
-        <v>17.25</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="O83" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P83" s="9">
         <v>9</v>
       </c>
-      <c r="Q83" s="9" t="s">
-        <v>257</v>
+      <c r="Q83" s="23" t="s">
+        <v>309</v>
       </c>
       <c r="R83" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="S83" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
+      </c>
+      <c r="S83" s="9" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6419,142 +6389,149 @@
         <v>254</v>
       </c>
       <c r="D84" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E84" s="12" t="s">
         <v>258</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>259</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G84" s="12">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H84" s="12">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I84" s="12">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="J84" s="17">
         <f t="shared" si="42"/>
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="K84" s="9">
         <f t="shared" si="43"/>
-        <v>16.5</v>
+        <v>21.5</v>
       </c>
       <c r="L84" s="10">
         <f t="shared" si="44"/>
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="M84" s="11">
         <f t="shared" si="45"/>
-        <v>72.5</v>
+        <v>68.75</v>
       </c>
       <c r="N84" s="11">
         <f t="shared" si="46"/>
-        <v>17.399999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="O84" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P84" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q84" s="23" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R84" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="S84" s="9" t="s">
-        <v>220</v>
+        <v>313</v>
+      </c>
+      <c r="S84" s="23" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="12" t="s">
-        <v>254</v>
+      <c r="C85" s="26" t="s">
+        <v>337</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>57</v>
+        <v>338</v>
+      </c>
+      <c r="E85" s="26" t="s">
+        <v>339</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>329</v>
       </c>
       <c r="G85" s="12">
+        <v>21</v>
+      </c>
+      <c r="H85" s="12">
         <v>20</v>
       </c>
-      <c r="H85" s="12">
-        <v>23</v>
-      </c>
       <c r="I85" s="12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J85" s="17">
         <f t="shared" si="42"/>
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="K85" s="9">
         <f t="shared" si="43"/>
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="L85" s="10">
         <f t="shared" si="44"/>
-        <v>73</v>
+        <v>72.5</v>
       </c>
       <c r="M85" s="11">
         <f t="shared" si="45"/>
-        <v>68.75</v>
+        <v>62.5</v>
       </c>
       <c r="N85" s="11">
         <f t="shared" si="46"/>
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="O85" s="9">
         <v>6</v>
       </c>
       <c r="P85" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q85" s="23" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="R85" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="S85" s="23" t="s">
-        <v>317</v>
+        <v>342</v>
+      </c>
+      <c r="S85" s="23"/>
+      <c r="U85" s="24" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C86" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="E86" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="F86" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="G86" s="12">
-        <v>21</v>
-      </c>
-      <c r="H86" s="12">
-        <v>20</v>
-      </c>
-      <c r="I86" s="12">
-        <v>10</v>
+      <c r="A86" s="3">
+        <v>80</v>
+      </c>
+      <c r="B86" s="3">
+        <v>75</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D86" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G86" s="5">
+        <v>27</v>
+      </c>
+      <c r="H86" s="5">
+        <v>14</v>
+      </c>
+      <c r="I86" s="5">
+        <v>12</v>
       </c>
       <c r="J86" s="17">
         <f t="shared" si="42"/>
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K86" s="9">
         <f t="shared" si="43"/>
@@ -6562,44 +6539,37 @@
       </c>
       <c r="L86" s="10">
         <f t="shared" si="44"/>
-        <v>72.5</v>
+        <v>81.5</v>
       </c>
       <c r="M86" s="11">
         <f t="shared" si="45"/>
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="N86" s="11">
         <f t="shared" si="46"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O86" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P86" s="9">
-        <v>8</v>
-      </c>
-      <c r="Q86" s="23" t="s">
-        <v>345</v>
+        <v>9</v>
+      </c>
+      <c r="Q86" s="9" t="s">
+        <v>262</v>
       </c>
       <c r="R86" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="S86" s="23"/>
-      <c r="U86" s="24" t="s">
-        <v>335</v>
+        <v>315</v>
+      </c>
+      <c r="S86" s="23" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
-        <v>80</v>
-      </c>
-      <c r="B87" s="3">
-        <v>75</v>
-      </c>
       <c r="C87" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D87" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="D87" s="5" t="s">
         <v>263</v>
       </c>
       <c r="E87" s="5" t="s">
@@ -6609,261 +6579,263 @@
         <v>57</v>
       </c>
       <c r="G87" s="5">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H87" s="5">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I87" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J87" s="17">
         <f t="shared" si="42"/>
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="K87" s="9">
         <f t="shared" si="43"/>
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="L87" s="10">
         <f t="shared" si="44"/>
-        <v>81.5</v>
+        <v>55.5</v>
       </c>
       <c r="M87" s="11">
         <f t="shared" si="45"/>
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="N87" s="11">
         <f t="shared" si="46"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O87" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P87" s="9">
-        <v>9</v>
-      </c>
-      <c r="Q87" s="9" t="s">
-        <v>265</v>
+        <v>6</v>
+      </c>
+      <c r="Q87" s="23" t="s">
+        <v>325</v>
       </c>
       <c r="R87" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="S87" s="23" t="s">
-        <v>319</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="S87" s="9"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>267</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>57</v>
       </c>
       <c r="G88" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H88" s="5">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I88" s="5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J88" s="17">
         <f t="shared" si="42"/>
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="K88" s="9">
         <f t="shared" si="43"/>
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
       <c r="L88" s="10">
         <f t="shared" si="44"/>
-        <v>55.5</v>
+        <v>60</v>
       </c>
       <c r="M88" s="11">
         <f t="shared" si="45"/>
-        <v>62.5</v>
+        <v>65.625</v>
       </c>
       <c r="N88" s="11">
         <f t="shared" si="46"/>
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="O88" s="9">
         <v>6</v>
       </c>
       <c r="P88" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q88" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="R88" s="23" t="s">
-        <v>321</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="R88" s="9"/>
       <c r="S88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D89" s="5" t="s">
+      <c r="A89" s="3">
+        <v>60</v>
+      </c>
+      <c r="B89" s="3">
+        <v>65</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D89" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E89" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G89" s="5">
-        <v>10</v>
-      </c>
-      <c r="H89" s="5">
-        <v>35</v>
-      </c>
-      <c r="I89" s="5">
+      <c r="G89" s="12">
+        <v>12</v>
+      </c>
+      <c r="H89" s="12">
+        <v>30</v>
+      </c>
+      <c r="I89" s="12">
         <v>10.5</v>
       </c>
       <c r="J89" s="17">
-        <f t="shared" si="42"/>
-        <v>37.5</v>
+        <f t="shared" ref="J89:J99" si="47">(G89*$I$2)+(H89*$I$3)</f>
+        <v>39</v>
       </c>
       <c r="K89" s="9">
-        <f t="shared" si="43"/>
-        <v>22.5</v>
+        <f t="shared" ref="K89:K111" si="48">(G89*$I$5)+(H89*$I$6)+(I89*$I$7)</f>
+        <v>21</v>
       </c>
       <c r="L89" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="L89:L99" si="49">J89+K89</f>
         <v>60</v>
       </c>
       <c r="M89" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="M89:M112" si="50">I89*$M$2</f>
         <v>65.625</v>
       </c>
       <c r="N89" s="11">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="N89:N112" si="51">I89*$M$3</f>
         <v>15.75</v>
       </c>
       <c r="O89" s="9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P89" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q89" s="23" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="R89" s="9"/>
       <c r="S89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
-        <v>60</v>
-      </c>
-      <c r="B90" s="3">
-        <v>65</v>
-      </c>
       <c r="C90" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="E90" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="F90" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G90" s="12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H90" s="12">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I90" s="12">
+        <v>7</v>
+      </c>
+      <c r="J90" s="17">
+        <f t="shared" si="47"/>
+        <v>27.5</v>
+      </c>
+      <c r="K90" s="9">
+        <f t="shared" si="48"/>
+        <v>12.5</v>
+      </c>
+      <c r="L90" s="10">
+        <f t="shared" si="49"/>
+        <v>40</v>
+      </c>
+      <c r="M90" s="11">
+        <f t="shared" si="50"/>
+        <v>43.75</v>
+      </c>
+      <c r="N90" s="11">
+        <f t="shared" si="51"/>
         <v>10.5</v>
-      </c>
-      <c r="J90" s="17">
-        <f t="shared" ref="J90:J100" si="47">(G90*$I$2)+(H90*$I$3)</f>
-        <v>39</v>
-      </c>
-      <c r="K90" s="9">
-        <f t="shared" ref="K90:K112" si="48">(G90*$I$5)+(H90*$I$6)+(I90*$I$7)</f>
-        <v>21</v>
-      </c>
-      <c r="L90" s="10">
-        <f t="shared" ref="L90:L100" si="49">J90+K90</f>
-        <v>60</v>
-      </c>
-      <c r="M90" s="11">
-        <f t="shared" ref="M90:M113" si="50">I90*$M$2</f>
-        <v>65.625</v>
-      </c>
-      <c r="N90" s="11">
-        <f t="shared" ref="N90:N113" si="51">I90*$M$3</f>
-        <v>15.75</v>
       </c>
       <c r="O90" s="9">
         <v>9</v>
       </c>
       <c r="P90" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q90" s="23" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="R90" s="9"/>
       <c r="S90" s="9"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C91" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="D91" s="21" t="s">
+      <c r="A91" s="3">
+        <v>75</v>
+      </c>
+      <c r="B91" s="3">
+        <v>80</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D91" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="E91" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F91" s="12" t="s">
+      <c r="F91" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G91" s="12">
-        <v>10</v>
-      </c>
-      <c r="H91" s="12">
-        <v>15</v>
-      </c>
-      <c r="I91" s="12">
-        <v>7</v>
+      <c r="G91" s="5">
+        <v>25</v>
+      </c>
+      <c r="H91" s="5">
+        <v>13</v>
+      </c>
+      <c r="I91" s="5">
+        <v>12.7</v>
       </c>
       <c r="J91" s="17">
         <f t="shared" si="47"/>
-        <v>27.5</v>
+        <v>56.5</v>
       </c>
       <c r="K91" s="9">
         <f t="shared" si="48"/>
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="L91" s="10">
         <f t="shared" si="49"/>
-        <v>40</v>
+        <v>75.5</v>
       </c>
       <c r="M91" s="11">
         <f t="shared" si="50"/>
-        <v>43.75</v>
+        <v>79.375</v>
       </c>
       <c r="N91" s="11">
         <f t="shared" si="51"/>
-        <v>10.5</v>
+        <v>19.049999999999997</v>
       </c>
       <c r="O91" s="9">
         <v>9</v>
@@ -6871,27 +6843,25 @@
       <c r="P91" s="9">
         <v>10</v>
       </c>
-      <c r="Q91" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="R91" s="9"/>
-      <c r="S91" s="9"/>
+      <c r="Q91" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="R91" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="S91" s="9" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
-        <v>75</v>
-      </c>
-      <c r="B92" s="3">
-        <v>80</v>
-      </c>
       <c r="C92" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>57</v>
@@ -6900,115 +6870,91 @@
         <v>25</v>
       </c>
       <c r="H92" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I92" s="5">
-        <v>12.7</v>
+        <v>12</v>
       </c>
       <c r="J92" s="17">
         <f t="shared" si="47"/>
-        <v>56.5</v>
+        <v>55</v>
       </c>
       <c r="K92" s="9">
         <f t="shared" si="48"/>
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="L92" s="10">
         <f t="shared" si="49"/>
-        <v>75.5</v>
+        <v>72.5</v>
       </c>
       <c r="M92" s="11">
         <f t="shared" si="50"/>
-        <v>79.375</v>
+        <v>75</v>
       </c>
       <c r="N92" s="11">
         <f t="shared" si="51"/>
-        <v>19.049999999999997</v>
+        <v>18</v>
       </c>
       <c r="O92" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P92" s="9">
-        <v>10</v>
-      </c>
-      <c r="Q92" s="3" t="s">
-        <v>278</v>
+        <v>12</v>
+      </c>
+      <c r="Q92" s="9" t="s">
+        <v>151</v>
       </c>
       <c r="R92" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="S92" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="S92" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="3">
+        <v>77</v>
+      </c>
+      <c r="B93" s="3">
+        <v>85</v>
+      </c>
+      <c r="C93" s="9" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G93" s="5">
-        <v>25</v>
-      </c>
-      <c r="H93" s="5">
-        <v>10</v>
-      </c>
-      <c r="I93" s="5">
-        <v>12</v>
-      </c>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="9"/>
+      <c r="I93" s="9"/>
       <c r="J93" s="17">
         <f t="shared" si="47"/>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K93" s="9">
         <f t="shared" si="48"/>
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="L93" s="10">
         <f t="shared" si="49"/>
-        <v>72.5</v>
+        <v>0</v>
       </c>
       <c r="M93" s="11">
         <f t="shared" si="50"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="N93" s="11">
         <f t="shared" si="51"/>
-        <v>18</v>
-      </c>
-      <c r="O93" s="9">
-        <v>8</v>
-      </c>
-      <c r="P93" s="9">
-        <v>12</v>
-      </c>
-      <c r="Q93" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="R93" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="S93" s="23" t="s">
-        <v>328</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O93" s="9"/>
+      <c r="P93" s="9"/>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
+      <c r="S93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
-        <v>77</v>
-      </c>
-      <c r="B94" s="3">
-        <v>85</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>282</v>
-      </c>
+      <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
@@ -7042,7 +6988,15 @@
       <c r="S94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="9"/>
+      <c r="A95" s="3">
+        <v>80</v>
+      </c>
+      <c r="B95" s="3">
+        <v>90</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>280</v>
+      </c>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
@@ -7076,15 +7030,7 @@
       <c r="S95" s="9"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
-        <v>80</v>
-      </c>
-      <c r="B96" s="3">
-        <v>90</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>283</v>
-      </c>
+      <c r="C96" s="9"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
@@ -7228,7 +7174,7 @@
       <c r="H100" s="9"/>
       <c r="I100" s="9"/>
       <c r="J100" s="17">
-        <f t="shared" si="47"/>
+        <f t="shared" ref="J100:J120" si="52">(G100*$I$2)+(H100*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K100" s="9">
@@ -7236,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="L100" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" ref="L100:L120" si="53">J100+K100</f>
         <v>0</v>
       </c>
       <c r="M100" s="11">
@@ -7262,7 +7208,7 @@
       <c r="H101" s="9"/>
       <c r="I101" s="9"/>
       <c r="J101" s="17">
-        <f t="shared" ref="J101:J121" si="52">(G101*$I$2)+(H101*$I$3)</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K101" s="9">
@@ -7270,7 +7216,7 @@
         <v>0</v>
       </c>
       <c r="L101" s="10">
-        <f t="shared" ref="L101:L121" si="53">J101+K101</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="M101" s="11">
@@ -7640,7 +7586,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="K112:K156" si="54">(G112*$I$5)+(H112*$I$6)+(I112*$I$7)</f>
         <v>0</v>
       </c>
       <c r="L112" s="10">
@@ -7674,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="9">
-        <f t="shared" ref="K113:K157" si="54">(G113*$I$5)+(H113*$I$6)+(I113*$I$7)</f>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L113" s="10">
@@ -7682,11 +7628,11 @@
         <v>0</v>
       </c>
       <c r="M113" s="11">
-        <f t="shared" si="50"/>
+        <f t="shared" ref="M113:M156" si="55">I113*$M$2</f>
         <v>0</v>
       </c>
       <c r="N113" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" ref="N113:N156" si="56">I113*$M$3</f>
         <v>0</v>
       </c>
       <c r="O113" s="9"/>
@@ -7716,11 +7662,11 @@
         <v>0</v>
       </c>
       <c r="M114" s="11">
-        <f t="shared" ref="M114:M157" si="55">I114*$M$2</f>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N114" s="11">
-        <f t="shared" ref="N114:N157" si="56">I114*$M$3</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="O114" s="9"/>
@@ -7942,7 +7888,7 @@
       <c r="H121" s="9"/>
       <c r="I121" s="9"/>
       <c r="J121" s="17">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="J121:J156" si="57">(G121*$I$2)+(H121*$I$3)</f>
         <v>0</v>
       </c>
       <c r="K121" s="9">
@@ -7950,7 +7896,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="L121:L156" si="58">J121+K121</f>
         <v>0</v>
       </c>
       <c r="M121" s="11">
@@ -7976,7 +7922,7 @@
       <c r="H122" s="9"/>
       <c r="I122" s="9"/>
       <c r="J122" s="17">
-        <f t="shared" ref="J122:J157" si="57">(G122*$I$2)+(H122*$I$3)</f>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="K122" s="9">
@@ -7984,7 +7930,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="10">
-        <f t="shared" ref="L122:L157" si="58">J122+K122</f>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="M122" s="11">
@@ -9156,40 +9102,6 @@
       <c r="Q156" s="9"/>
       <c r="R156" s="9"/>
       <c r="S156" s="9"/>
-    </row>
-    <row r="157" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C157" s="9"/>
-      <c r="D157" s="9"/>
-      <c r="E157" s="9"/>
-      <c r="F157" s="9"/>
-      <c r="G157" s="9"/>
-      <c r="H157" s="9"/>
-      <c r="I157" s="9"/>
-      <c r="J157" s="17">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="K157" s="9">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="L157" s="10">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="M157" s="11">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="N157" s="11">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="O157" s="9"/>
-      <c r="P157" s="9"/>
-      <c r="Q157" s="9"/>
-      <c r="R157" s="9"/>
-      <c r="S157" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -9246,15 +9158,15 @@
         <v>49</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C2" s="5">
         <v>7</v>
@@ -9272,10 +9184,10 @@
         <v>4</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11">
@@ -9285,10 +9197,10 @@
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C3" s="5">
         <v>15</v>
@@ -9306,10 +9218,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11">
@@ -9319,10 +9231,10 @@
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C4" s="12">
         <v>21</v>
@@ -9340,10 +9252,10 @@
         <v>8</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11">
@@ -9725,45 +9637,45 @@
   <sheetData>
     <row r="5" spans="4:19" x14ac:dyDescent="0.2">
       <c r="F5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5" t="s">
+        <v>282</v>
+      </c>
+      <c r="J5" t="s">
+        <v>283</v>
+      </c>
+      <c r="M5" t="s">
         <v>284</v>
-      </c>
-      <c r="G5" t="s">
-        <v>285</v>
-      </c>
-      <c r="J5" t="s">
-        <v>286</v>
-      </c>
-      <c r="M5" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="6" spans="4:19" x14ac:dyDescent="0.2">
       <c r="F6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G6" t="s">
+        <v>285</v>
+      </c>
+      <c r="H6" t="s">
+        <v>286</v>
+      </c>
+      <c r="I6" t="s">
+        <v>287</v>
+      </c>
+      <c r="J6" t="s">
         <v>288</v>
       </c>
-      <c r="G6" t="s">
-        <v>288</v>
-      </c>
-      <c r="H6" t="s">
-        <v>289</v>
-      </c>
-      <c r="I6" t="s">
-        <v>290</v>
-      </c>
-      <c r="J6" t="s">
-        <v>291</v>
-      </c>
       <c r="K6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="L6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="M6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -9771,7 +9683,7 @@
     </row>
     <row r="7" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
@@ -9858,7 +9770,7 @@
     </row>
     <row r="10" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
@@ -9949,7 +9861,7 @@
     </row>
     <row r="12" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>-0.1</v>
@@ -9985,7 +9897,7 @@
     </row>
     <row r="13" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F13">
         <v>-15</v>
